--- a/02_실전캠프_Day2_실습제출/3조_강상구_숯불에닭/v2/프로젝트/public/sample/가짜_거래내역_2026-09.xlsx
+++ b/02_실전캠프_Day2_실습제출/3조_강상구_숯불에닭/v2/프로젝트/public/sample/가짜_거래내역_2026-09.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G61"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -524,16 +524,16 @@
         <v>타행이체</v>
       </c>
       <c r="C8" t="str">
-        <v>BC카드매출</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D8" t="str">
         <v/>
       </c>
       <c r="E8">
-        <v>450000</v>
+        <v>33480</v>
       </c>
       <c r="F8">
-        <v>7830000</v>
+        <v>7413480</v>
       </c>
       <c r="G8" t="str">
         <v>가짜지점</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-09-03 13:44:00</v>
+        <v>2026-09-02 13:44:00</v>
       </c>
       <c r="B9" t="str">
         <v>타행이체</v>
@@ -553,10 +553,10 @@
         <v/>
       </c>
       <c r="E9">
-        <v>410020</v>
+        <v>450000</v>
       </c>
       <c r="F9">
-        <v>8240020</v>
+        <v>7863480</v>
       </c>
       <c r="G9" t="str">
         <v>가짜지점</v>
@@ -567,19 +567,19 @@
         <v>2026-09-03 14:55:00</v>
       </c>
       <c r="B10" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C10" t="str">
-        <v>가나식품</v>
-      </c>
-      <c r="D10">
-        <v>1500000</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
+        <v>BC카드매출</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10">
+        <v>410020</v>
       </c>
       <c r="F10">
-        <v>6740020</v>
+        <v>8273500</v>
       </c>
       <c r="G10" t="str">
         <v>가짜지점</v>
@@ -587,7 +587,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-09-04 15:06:00</v>
+        <v>2026-09-03 15:06:00</v>
       </c>
       <c r="B11" t="str">
         <v>타행이체</v>
@@ -599,10 +599,10 @@
         <v/>
       </c>
       <c r="E11">
-        <v>33480</v>
+        <v>38130</v>
       </c>
       <c r="F11">
-        <v>6773500</v>
+        <v>8311630</v>
       </c>
       <c r="G11" t="str">
         <v>가짜지점</v>
@@ -610,22 +610,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-09-04 16:17:00</v>
+        <v>2026-09-03 16:17:00</v>
       </c>
       <c r="B12" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C12" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12">
-        <v>468312</v>
+        <v>가나식품</v>
+      </c>
+      <c r="D12">
+        <v>1500000</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
       </c>
       <c r="F12">
-        <v>7241812</v>
+        <v>6811630</v>
       </c>
       <c r="G12" t="str">
         <v>가짜지점</v>
@@ -633,22 +633,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-09-05 17:28:00</v>
+        <v>2026-09-04 17:28:00</v>
       </c>
       <c r="B13" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C13" t="str">
-        <v>숯닭본사(가맹)</v>
-      </c>
-      <c r="D13">
-        <v>1200000</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
+        <v>우아한형제들</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13">
+        <v>257550</v>
       </c>
       <c r="F13">
-        <v>6041812</v>
+        <v>7069180</v>
       </c>
       <c r="G13" t="str">
         <v>가짜지점</v>
@@ -656,22 +656,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-09-07 09:39:00</v>
+        <v>2026-09-04 09:39:00</v>
       </c>
       <c r="B14" t="str">
         <v>타행이체</v>
       </c>
       <c r="C14" t="str">
-        <v>우아한형제들</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D14" t="str">
         <v/>
       </c>
       <c r="E14">
-        <v>2021300</v>
+        <v>468312</v>
       </c>
       <c r="F14">
-        <v>8063112</v>
+        <v>7537492</v>
       </c>
       <c r="G14" t="str">
         <v>가짜지점</v>
@@ -679,7 +679,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-09-07 10:50:00</v>
+        <v>2026-09-04 10:50:00</v>
       </c>
       <c r="B15" t="str">
         <v>타행이체</v>
@@ -691,10 +691,10 @@
         <v/>
       </c>
       <c r="E15">
-        <v>38130</v>
+        <v>36270</v>
       </c>
       <c r="F15">
-        <v>8101242</v>
+        <v>7573762</v>
       </c>
       <c r="G15" t="str">
         <v>가짜지점</v>
@@ -702,22 +702,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-09-07 11:01:00</v>
+        <v>2026-09-05 11:01:00</v>
       </c>
       <c r="B16" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C16" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16">
-        <v>450528</v>
+        <v>숯닭본사(가맹)</v>
+      </c>
+      <c r="D16">
+        <v>1200000</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
       </c>
       <c r="F16">
-        <v>8551770</v>
+        <v>6373762</v>
       </c>
       <c r="G16" t="str">
         <v>가짜지점</v>
@@ -725,22 +725,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-09-08 12:12:00</v>
+        <v>2026-09-07 12:12:00</v>
       </c>
       <c r="B17" t="str">
         <v>타행이체</v>
       </c>
       <c r="C17" t="str">
-        <v>요기요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D17" t="str">
         <v/>
       </c>
       <c r="E17">
-        <v>61920</v>
+        <v>294100</v>
       </c>
       <c r="F17">
-        <v>8613690</v>
+        <v>6667862</v>
       </c>
       <c r="G17" t="str">
         <v>가짜지점</v>
@@ -748,22 +748,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-09-08 13:23:00</v>
+        <v>2026-09-07 13:23:00</v>
       </c>
       <c r="B18" t="str">
         <v>타행이체</v>
       </c>
       <c r="C18" t="str">
-        <v>땡겨요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18">
-        <v>36270</v>
+        <v>450528</v>
       </c>
       <c r="F18">
-        <v>8649960</v>
+        <v>7118390</v>
       </c>
       <c r="G18" t="str">
         <v>가짜지점</v>
@@ -771,22 +771,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-09-08 14:34:00</v>
+        <v>2026-09-07 14:34:00</v>
       </c>
       <c r="B19" t="str">
         <v>타행이체</v>
       </c>
       <c r="C19" t="str">
-        <v>BC카드매출</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D19" t="str">
         <v/>
       </c>
       <c r="E19">
-        <v>1887080</v>
+        <v>153450</v>
       </c>
       <c r="F19">
-        <v>10537040</v>
+        <v>7271840</v>
       </c>
       <c r="G19" t="str">
         <v>가짜지점</v>
@@ -797,19 +797,19 @@
         <v>2026-09-08 15:45:00</v>
       </c>
       <c r="B20" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C20" t="str">
-        <v>참숯나라</v>
-      </c>
-      <c r="D20">
-        <v>450000</v>
-      </c>
-      <c r="E20" t="str">
-        <v/>
+        <v>요기요정산</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20">
+        <v>61920</v>
       </c>
       <c r="F20">
-        <v>10087040</v>
+        <v>7333760</v>
       </c>
       <c r="G20" t="str">
         <v>가짜지점</v>
@@ -817,22 +817,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-09-09 16:56:00</v>
+        <v>2026-09-08 16:56:00</v>
       </c>
       <c r="B21" t="str">
         <v>타행이체</v>
       </c>
       <c r="C21" t="str">
-        <v>요기요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D21" t="str">
         <v/>
       </c>
       <c r="E21">
-        <v>70520</v>
+        <v>283050</v>
       </c>
       <c r="F21">
-        <v>10157560</v>
+        <v>7616810</v>
       </c>
       <c r="G21" t="str">
         <v>가짜지점</v>
@@ -840,22 +840,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-09-09 17:07:00</v>
+        <v>2026-09-08 17:07:00</v>
       </c>
       <c r="B22" t="str">
         <v>타행이체</v>
       </c>
       <c r="C22" t="str">
-        <v>땡겨요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D22" t="str">
         <v/>
       </c>
       <c r="E22">
-        <v>153450</v>
+        <v>1887080</v>
       </c>
       <c r="F22">
-        <v>10311010</v>
+        <v>9503890</v>
       </c>
       <c r="G22" t="str">
         <v>가짜지점</v>
@@ -863,22 +863,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-09-09 09:18:00</v>
+        <v>2026-09-08 09:18:00</v>
       </c>
       <c r="B23" t="str">
         <v>타행이체</v>
       </c>
       <c r="C23" t="str">
-        <v>BC카드매출</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D23" t="str">
         <v/>
       </c>
       <c r="E23">
-        <v>400140</v>
+        <v>32550</v>
       </c>
       <c r="F23">
-        <v>10711150</v>
+        <v>9536440</v>
       </c>
       <c r="G23" t="str">
         <v>가짜지점</v>
@@ -886,22 +886,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-09-10 10:29:00</v>
+        <v>2026-09-08 10:29:00</v>
       </c>
       <c r="B24" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C24" t="str">
-        <v>요기요정산</v>
-      </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-      <c r="E24">
-        <v>67940</v>
+        <v>참숯나라</v>
+      </c>
+      <c r="D24">
+        <v>450000</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
       </c>
       <c r="F24">
-        <v>10779090</v>
+        <v>9086440</v>
       </c>
       <c r="G24" t="str">
         <v>가짜지점</v>
@@ -909,22 +909,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-09-10 11:40:00</v>
+        <v>2026-09-09 11:40:00</v>
       </c>
       <c r="B25" t="str">
         <v>타행이체</v>
       </c>
       <c r="C25" t="str">
-        <v>땡겨요정산</v>
+        <v>요기요정산</v>
       </c>
       <c r="D25" t="str">
         <v/>
       </c>
       <c r="E25">
-        <v>32550</v>
+        <v>70520</v>
       </c>
       <c r="F25">
-        <v>10811640</v>
+        <v>9156960</v>
       </c>
       <c r="G25" t="str">
         <v>가짜지점</v>
@@ -932,22 +932,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-09-10 12:51:00</v>
+        <v>2026-09-09 12:51:00</v>
       </c>
       <c r="B26" t="str">
         <v>타행이체</v>
       </c>
       <c r="C26" t="str">
-        <v>BC카드매출</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D26" t="str">
         <v/>
       </c>
       <c r="E26">
-        <v>442624</v>
+        <v>1186600</v>
       </c>
       <c r="F26">
-        <v>11254264</v>
+        <v>10343560</v>
       </c>
       <c r="G26" t="str">
         <v>가짜지점</v>
@@ -955,22 +955,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-09-10 13:02:00</v>
+        <v>2026-09-09 13:02:00</v>
       </c>
       <c r="B27" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C27" t="str">
-        <v>가나식품</v>
-      </c>
-      <c r="D27">
-        <v>1450000</v>
-      </c>
-      <c r="E27" t="str">
-        <v/>
+        <v>BC카드매출</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27">
+        <v>400140</v>
       </c>
       <c r="F27">
-        <v>9804264</v>
+        <v>10743700</v>
       </c>
       <c r="G27" t="str">
         <v>가짜지점</v>
@@ -978,22 +978,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-09-10 14:13:00</v>
+        <v>2026-09-09 14:13:00</v>
       </c>
       <c r="B28" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C28" t="str">
-        <v>급여(주방)</v>
-      </c>
-      <c r="D28">
-        <v>2800000</v>
-      </c>
-      <c r="E28" t="str">
-        <v/>
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28">
+        <v>36270</v>
       </c>
       <c r="F28">
-        <v>7004264</v>
+        <v>10779970</v>
       </c>
       <c r="G28" t="str">
         <v>가짜지점</v>
@@ -1001,22 +1001,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-09-11 15:24:00</v>
+        <v>2026-09-10 15:24:00</v>
       </c>
       <c r="B29" t="str">
         <v>타행이체</v>
       </c>
       <c r="C29" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>요기요정산</v>
       </c>
       <c r="D29" t="str">
         <v/>
       </c>
       <c r="E29">
-        <v>1077480</v>
+        <v>67940</v>
       </c>
       <c r="F29">
-        <v>8081744</v>
+        <v>10847910</v>
       </c>
       <c r="G29" t="str">
         <v>가짜지점</v>
@@ -1024,22 +1024,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-09-11 16:35:00</v>
+        <v>2026-09-10 16:35:00</v>
       </c>
       <c r="B30" t="str">
         <v>타행이체</v>
       </c>
       <c r="C30" t="str">
-        <v>요기요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D30" t="str">
         <v/>
       </c>
       <c r="E30">
-        <v>284660</v>
+        <v>251600</v>
       </c>
       <c r="F30">
-        <v>8366404</v>
+        <v>11099510</v>
       </c>
       <c r="G30" t="str">
         <v>가짜지점</v>
@@ -1047,22 +1047,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-09-11 17:46:00</v>
+        <v>2026-09-10 17:46:00</v>
       </c>
       <c r="B31" t="str">
         <v>타행이체</v>
       </c>
       <c r="C31" t="str">
-        <v>땡겨요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D31" t="str">
         <v/>
       </c>
       <c r="E31">
-        <v>36270</v>
+        <v>442624</v>
       </c>
       <c r="F31">
-        <v>8402674</v>
+        <v>11542134</v>
       </c>
       <c r="G31" t="str">
         <v>가짜지점</v>
@@ -1070,22 +1070,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-09-11 09:57:00</v>
+        <v>2026-09-10 09:57:00</v>
       </c>
       <c r="B32" t="str">
         <v>타행이체</v>
       </c>
       <c r="C32" t="str">
-        <v>BC카드매출</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D32" t="str">
         <v/>
       </c>
       <c r="E32">
-        <v>470288</v>
+        <v>38130</v>
       </c>
       <c r="F32">
-        <v>8872962</v>
+        <v>11580264</v>
       </c>
       <c r="G32" t="str">
         <v>가짜지점</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-09-14 10:08:00</v>
+        <v>2026-09-10 10:08:00</v>
       </c>
       <c r="B33" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C33" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D33" t="str">
-        <v/>
-      </c>
-      <c r="E33">
-        <v>2357900</v>
+        <v>가나식품</v>
+      </c>
+      <c r="D33">
+        <v>1450000</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
       </c>
       <c r="F33">
-        <v>11230862</v>
+        <v>10130264</v>
       </c>
       <c r="G33" t="str">
         <v>가짜지점</v>
@@ -1116,22 +1116,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-09-14 11:19:00</v>
+        <v>2026-09-10 11:19:00</v>
       </c>
       <c r="B34" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C34" t="str">
-        <v>요기요정산</v>
-      </c>
-      <c r="D34" t="str">
-        <v/>
-      </c>
-      <c r="E34">
-        <v>60200</v>
+        <v>급여(주방)</v>
+      </c>
+      <c r="D34">
+        <v>2800000</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
       </c>
       <c r="F34">
-        <v>11291062</v>
+        <v>7330264</v>
       </c>
       <c r="G34" t="str">
         <v>가짜지점</v>
@@ -1139,22 +1139,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-09-14 12:30:00</v>
+        <v>2026-09-11 12:30:00</v>
       </c>
       <c r="B35" t="str">
         <v>타행이체</v>
       </c>
       <c r="C35" t="str">
-        <v>땡겨요정산</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D35" t="str">
         <v/>
       </c>
       <c r="E35">
-        <v>38130</v>
+        <v>1077480</v>
       </c>
       <c r="F35">
-        <v>11329192</v>
+        <v>8407744</v>
       </c>
       <c r="G35" t="str">
         <v>가짜지점</v>
@@ -1162,22 +1162,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-09-14 13:41:00</v>
+        <v>2026-09-11 13:41:00</v>
       </c>
       <c r="B36" t="str">
         <v>타행이체</v>
       </c>
       <c r="C36" t="str">
-        <v>BC카드매출</v>
+        <v>요기요정산</v>
       </c>
       <c r="D36" t="str">
         <v/>
       </c>
       <c r="E36">
-        <v>479180</v>
+        <v>284660</v>
       </c>
       <c r="F36">
-        <v>11808372</v>
+        <v>8692404</v>
       </c>
       <c r="G36" t="str">
         <v>가짜지점</v>
@@ -1185,22 +1185,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-09-15 14:52:00</v>
+        <v>2026-09-11 14:52:00</v>
       </c>
       <c r="B37" t="str">
         <v>타행이체</v>
       </c>
       <c r="C37" t="str">
-        <v>요기요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D37" t="str">
         <v/>
       </c>
       <c r="E37">
-        <v>66220</v>
+        <v>277950</v>
       </c>
       <c r="F37">
-        <v>11874592</v>
+        <v>8970354</v>
       </c>
       <c r="G37" t="str">
         <v>가짜지점</v>
@@ -1208,22 +1208,22 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-09-15 15:03:00</v>
+        <v>2026-09-11 15:03:00</v>
       </c>
       <c r="B38" t="str">
         <v>타행이체</v>
       </c>
       <c r="C38" t="str">
-        <v>땡겨요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D38" t="str">
         <v/>
       </c>
       <c r="E38">
-        <v>39060</v>
+        <v>470288</v>
       </c>
       <c r="F38">
-        <v>11913652</v>
+        <v>9440642</v>
       </c>
       <c r="G38" t="str">
         <v>가짜지점</v>
@@ -1231,22 +1231,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-09-15 16:14:00</v>
+        <v>2026-09-11 16:14:00</v>
       </c>
       <c r="B39" t="str">
         <v>타행이체</v>
       </c>
       <c r="C39" t="str">
-        <v>BC카드매출</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D39" t="str">
         <v/>
       </c>
       <c r="E39">
-        <v>1957228</v>
+        <v>39060</v>
       </c>
       <c r="F39">
-        <v>13870880</v>
+        <v>9479702</v>
       </c>
       <c r="G39" t="str">
         <v>가짜지점</v>
@@ -1254,22 +1254,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-09-15 17:25:00</v>
+        <v>2026-09-14 17:25:00</v>
       </c>
       <c r="B40" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C40" t="str">
-        <v>생활비이체</v>
-      </c>
-      <c r="D40">
-        <v>2500000</v>
-      </c>
-      <c r="E40" t="str">
-        <v/>
+        <v>요기요정산</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40">
+        <v>60200</v>
       </c>
       <c r="F40">
-        <v>11370880</v>
+        <v>9539902</v>
       </c>
       <c r="G40" t="str">
         <v>가짜지점</v>
@@ -1277,22 +1277,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-09-16 09:36:00</v>
+        <v>2026-09-14 09:36:00</v>
       </c>
       <c r="B41" t="str">
         <v>타행이체</v>
       </c>
       <c r="C41" t="str">
-        <v>요기요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D41" t="str">
         <v/>
       </c>
       <c r="E41">
-        <v>70520</v>
+        <v>295800</v>
       </c>
       <c r="F41">
-        <v>11441400</v>
+        <v>9835702</v>
       </c>
       <c r="G41" t="str">
         <v>가짜지점</v>
@@ -1300,22 +1300,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-09-16 10:47:00</v>
+        <v>2026-09-14 10:47:00</v>
       </c>
       <c r="B42" t="str">
         <v>타행이체</v>
       </c>
       <c r="C42" t="str">
-        <v>땡겨요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D42" t="str">
         <v/>
       </c>
       <c r="E42">
-        <v>159960</v>
+        <v>479180</v>
       </c>
       <c r="F42">
-        <v>11601360</v>
+        <v>10314882</v>
       </c>
       <c r="G42" t="str">
         <v>가짜지점</v>
@@ -1323,22 +1323,22 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-09-16 11:58:00</v>
+        <v>2026-09-14 11:58:00</v>
       </c>
       <c r="B43" t="str">
         <v>타행이체</v>
       </c>
       <c r="C43" t="str">
-        <v>BC카드매출</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D43" t="str">
         <v/>
       </c>
       <c r="E43">
-        <v>400140</v>
+        <v>159960</v>
       </c>
       <c r="F43">
-        <v>12001500</v>
+        <v>10474842</v>
       </c>
       <c r="G43" t="str">
         <v>가짜지점</v>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-09-17 12:09:00</v>
+        <v>2026-09-15 12:09:00</v>
       </c>
       <c r="B44" t="str">
         <v>타행이체</v>
@@ -1358,10 +1358,10 @@
         <v/>
       </c>
       <c r="E44">
-        <v>72240</v>
+        <v>66220</v>
       </c>
       <c r="F44">
-        <v>12073740</v>
+        <v>10541062</v>
       </c>
       <c r="G44" t="str">
         <v>가짜지점</v>
@@ -1369,22 +1369,22 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-09-17 13:20:00</v>
+        <v>2026-09-15 13:20:00</v>
       </c>
       <c r="B45" t="str">
         <v>타행이체</v>
       </c>
       <c r="C45" t="str">
-        <v>땡겨요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D45" t="str">
         <v/>
       </c>
       <c r="E45">
-        <v>32550</v>
+        <v>301750</v>
       </c>
       <c r="F45">
-        <v>12106290</v>
+        <v>10842812</v>
       </c>
       <c r="G45" t="str">
         <v>가짜지점</v>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-09-17 14:31:00</v>
+        <v>2026-09-15 14:31:00</v>
       </c>
       <c r="B46" t="str">
         <v>타행이체</v>
@@ -1404,10 +1404,10 @@
         <v/>
       </c>
       <c r="E46">
-        <v>411008</v>
+        <v>1957228</v>
       </c>
       <c r="F46">
-        <v>12517298</v>
+        <v>12800040</v>
       </c>
       <c r="G46" t="str">
         <v>가짜지점</v>
@@ -1415,22 +1415,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-09-18 15:42:00</v>
+        <v>2026-09-15 15:42:00</v>
       </c>
       <c r="B47" t="str">
         <v>타행이체</v>
       </c>
       <c r="C47" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D47" t="str">
         <v/>
       </c>
       <c r="E47">
-        <v>1226240</v>
+        <v>32550</v>
       </c>
       <c r="F47">
-        <v>13743538</v>
+        <v>12832590</v>
       </c>
       <c r="G47" t="str">
         <v>가짜지점</v>
@@ -1438,22 +1438,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-09-18 16:53:00</v>
+        <v>2026-09-15 16:53:00</v>
       </c>
       <c r="B48" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C48" t="str">
-        <v>요기요정산</v>
-      </c>
-      <c r="D48" t="str">
-        <v/>
-      </c>
-      <c r="E48">
-        <v>294980</v>
+        <v>생활비이체</v>
+      </c>
+      <c r="D48">
+        <v>2500000</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
       </c>
       <c r="F48">
-        <v>14038518</v>
+        <v>10332590</v>
       </c>
       <c r="G48" t="str">
         <v>가짜지점</v>
@@ -1461,22 +1461,22 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-09-18 17:04:00</v>
+        <v>2026-09-16 17:04:00</v>
       </c>
       <c r="B49" t="str">
         <v>타행이체</v>
       </c>
       <c r="C49" t="str">
-        <v>땡겨요정산</v>
+        <v>요기요정산</v>
       </c>
       <c r="D49" t="str">
         <v/>
       </c>
       <c r="E49">
-        <v>33480</v>
+        <v>70520</v>
       </c>
       <c r="F49">
-        <v>14071998</v>
+        <v>10403110</v>
       </c>
       <c r="G49" t="str">
         <v>가짜지점</v>
@@ -1484,30 +1484,283 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-09-18 09:15:00</v>
+        <v>2026-09-16 09:15:00</v>
       </c>
       <c r="B50" t="str">
         <v>타행이체</v>
       </c>
       <c r="C50" t="str">
+        <v>우아한형제들</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50">
+        <v>1230800</v>
+      </c>
+      <c r="F50">
+        <v>11633910</v>
+      </c>
+      <c r="G50" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-09-16 10:26:00</v>
+      </c>
+      <c r="B51" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C51" t="str">
         <v>BC카드매출</v>
       </c>
-      <c r="D50" t="str">
-        <v/>
-      </c>
-      <c r="E50">
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51">
+        <v>400140</v>
+      </c>
+      <c r="F51">
+        <v>12034050</v>
+      </c>
+      <c r="G51" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-09-16 11:37:00</v>
+      </c>
+      <c r="B52" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C52" t="str">
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52">
+        <v>33480</v>
+      </c>
+      <c r="F52">
+        <v>12067530</v>
+      </c>
+      <c r="G52" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-09-17 12:48:00</v>
+      </c>
+      <c r="B53" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C53" t="str">
+        <v>요기요정산</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53">
+        <v>72240</v>
+      </c>
+      <c r="F53">
+        <v>12139770</v>
+      </c>
+      <c r="G53" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-09-17 13:59:00</v>
+      </c>
+      <c r="B54" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C54" t="str">
+        <v>우아한형제들</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54">
+        <v>251600</v>
+      </c>
+      <c r="F54">
+        <v>12391370</v>
+      </c>
+      <c r="G54" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-09-17 14:10:00</v>
+      </c>
+      <c r="B55" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C55" t="str">
+        <v>BC카드매출</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55">
+        <v>411008</v>
+      </c>
+      <c r="F55">
+        <v>12802378</v>
+      </c>
+      <c r="G55" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-09-17 15:21:00</v>
+      </c>
+      <c r="B56" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C56" t="str">
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56">
+        <v>35340</v>
+      </c>
+      <c r="F56">
+        <v>12837718</v>
+      </c>
+      <c r="G56" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-09-18 16:32:00</v>
+      </c>
+      <c r="B57" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C57" t="str">
+        <v>쿠팡이츠정산</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57">
+        <v>1226240</v>
+      </c>
+      <c r="F57">
+        <v>14063958</v>
+      </c>
+      <c r="G57" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-09-18 17:43:00</v>
+      </c>
+      <c r="B58" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C58" t="str">
+        <v>요기요정산</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58">
+        <v>294980</v>
+      </c>
+      <c r="F58">
+        <v>14358938</v>
+      </c>
+      <c r="G58" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2026-09-18 09:54:00</v>
+      </c>
+      <c r="B59" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C59" t="str">
+        <v>우아한형제들</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59">
+        <v>258400</v>
+      </c>
+      <c r="F59">
+        <v>14617338</v>
+      </c>
+      <c r="G59" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-09-18 10:05:00</v>
+      </c>
+      <c r="B60" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C60" t="str">
+        <v>BC카드매출</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60">
         <v>437684</v>
       </c>
-      <c r="F50">
-        <v>14509682</v>
-      </c>
-      <c r="G50" t="str">
+      <c r="F60">
+        <v>15055022</v>
+      </c>
+      <c r="G60" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2026-09-18 11:16:00</v>
+      </c>
+      <c r="B61" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C61" t="str">
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61">
+        <v>40920</v>
+      </c>
+      <c r="F61">
+        <v>15095942</v>
+      </c>
+      <c r="G61" t="str">
         <v>가짜지점</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/02_실전캠프_Day2_실습제출/3조_강상구_숯불에닭/v2/프로젝트/public/sample/가짜_거래내역_2026-09.xlsx
+++ b/02_실전캠프_Day2_실습제출/3조_강상구_숯불에닭/v2/프로젝트/public/sample/가짜_거래내역_2026-09.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G69"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -731,16 +731,16 @@
         <v>타행이체</v>
       </c>
       <c r="C17" t="str">
-        <v>우아한형제들</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D17" t="str">
         <v/>
       </c>
       <c r="E17">
-        <v>294100</v>
+        <v>137760</v>
       </c>
       <c r="F17">
-        <v>6667862</v>
+        <v>6511522</v>
       </c>
       <c r="G17" t="str">
         <v>가짜지점</v>
@@ -754,16 +754,16 @@
         <v>타행이체</v>
       </c>
       <c r="C18" t="str">
-        <v>BC카드매출</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18">
-        <v>450528</v>
+        <v>294100</v>
       </c>
       <c r="F18">
-        <v>7118390</v>
+        <v>6805622</v>
       </c>
       <c r="G18" t="str">
         <v>가짜지점</v>
@@ -777,16 +777,16 @@
         <v>타행이체</v>
       </c>
       <c r="C19" t="str">
-        <v>땡겨요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D19" t="str">
         <v/>
       </c>
       <c r="E19">
-        <v>153450</v>
+        <v>450528</v>
       </c>
       <c r="F19">
-        <v>7271840</v>
+        <v>7256150</v>
       </c>
       <c r="G19" t="str">
         <v>가짜지점</v>
@@ -794,22 +794,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-09-08 15:45:00</v>
+        <v>2026-09-07 15:45:00</v>
       </c>
       <c r="B20" t="str">
         <v>타행이체</v>
       </c>
       <c r="C20" t="str">
-        <v>요기요정산</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D20" t="str">
         <v/>
       </c>
       <c r="E20">
-        <v>61920</v>
+        <v>153450</v>
       </c>
       <c r="F20">
-        <v>7333760</v>
+        <v>7409600</v>
       </c>
       <c r="G20" t="str">
         <v>가짜지점</v>
@@ -823,16 +823,16 @@
         <v>타행이체</v>
       </c>
       <c r="C21" t="str">
-        <v>우아한형제들</v>
+        <v>요기요정산</v>
       </c>
       <c r="D21" t="str">
         <v/>
       </c>
       <c r="E21">
-        <v>283050</v>
+        <v>61920</v>
       </c>
       <c r="F21">
-        <v>7616810</v>
+        <v>7471520</v>
       </c>
       <c r="G21" t="str">
         <v>가짜지점</v>
@@ -846,16 +846,16 @@
         <v>타행이체</v>
       </c>
       <c r="C22" t="str">
-        <v>BC카드매출</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D22" t="str">
         <v/>
       </c>
       <c r="E22">
-        <v>1887080</v>
+        <v>126620</v>
       </c>
       <c r="F22">
-        <v>9503890</v>
+        <v>7598140</v>
       </c>
       <c r="G22" t="str">
         <v>가짜지점</v>
@@ -869,16 +869,16 @@
         <v>타행이체</v>
       </c>
       <c r="C23" t="str">
-        <v>땡겨요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D23" t="str">
         <v/>
       </c>
       <c r="E23">
-        <v>32550</v>
+        <v>283050</v>
       </c>
       <c r="F23">
-        <v>9536440</v>
+        <v>7881190</v>
       </c>
       <c r="G23" t="str">
         <v>가짜지점</v>
@@ -889,19 +889,19 @@
         <v>2026-09-08 10:29:00</v>
       </c>
       <c r="B24" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C24" t="str">
-        <v>참숯나라</v>
-      </c>
-      <c r="D24">
-        <v>450000</v>
-      </c>
-      <c r="E24" t="str">
-        <v/>
+        <v>BC카드매출</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24">
+        <v>1887080</v>
       </c>
       <c r="F24">
-        <v>9086440</v>
+        <v>9768270</v>
       </c>
       <c r="G24" t="str">
         <v>가짜지점</v>
@@ -909,22 +909,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-09-09 11:40:00</v>
+        <v>2026-09-08 11:40:00</v>
       </c>
       <c r="B25" t="str">
         <v>타행이체</v>
       </c>
       <c r="C25" t="str">
-        <v>요기요정산</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D25" t="str">
         <v/>
       </c>
       <c r="E25">
-        <v>70520</v>
+        <v>32550</v>
       </c>
       <c r="F25">
-        <v>9156960</v>
+        <v>9800820</v>
       </c>
       <c r="G25" t="str">
         <v>가짜지점</v>
@@ -932,22 +932,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-09-09 12:51:00</v>
+        <v>2026-09-08 12:51:00</v>
       </c>
       <c r="B26" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C26" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D26" t="str">
-        <v/>
-      </c>
-      <c r="E26">
-        <v>1186600</v>
+        <v>참숯나라</v>
+      </c>
+      <c r="D26">
+        <v>450000</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
       </c>
       <c r="F26">
-        <v>10343560</v>
+        <v>9350820</v>
       </c>
       <c r="G26" t="str">
         <v>가짜지점</v>
@@ -961,16 +961,16 @@
         <v>타행이체</v>
       </c>
       <c r="C27" t="str">
-        <v>BC카드매출</v>
+        <v>요기요정산</v>
       </c>
       <c r="D27" t="str">
         <v/>
       </c>
       <c r="E27">
-        <v>400140</v>
+        <v>70520</v>
       </c>
       <c r="F27">
-        <v>10743700</v>
+        <v>9421340</v>
       </c>
       <c r="G27" t="str">
         <v>가짜지점</v>
@@ -984,16 +984,16 @@
         <v>타행이체</v>
       </c>
       <c r="C28" t="str">
-        <v>땡겨요정산</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D28" t="str">
         <v/>
       </c>
       <c r="E28">
-        <v>36270</v>
+        <v>150880</v>
       </c>
       <c r="F28">
-        <v>10779970</v>
+        <v>9572220</v>
       </c>
       <c r="G28" t="str">
         <v>가짜지점</v>
@@ -1001,22 +1001,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-09-10 15:24:00</v>
+        <v>2026-09-09 15:24:00</v>
       </c>
       <c r="B29" t="str">
         <v>타행이체</v>
       </c>
       <c r="C29" t="str">
-        <v>요기요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D29" t="str">
         <v/>
       </c>
       <c r="E29">
-        <v>67940</v>
+        <v>1186600</v>
       </c>
       <c r="F29">
-        <v>10847910</v>
+        <v>10758820</v>
       </c>
       <c r="G29" t="str">
         <v>가짜지점</v>
@@ -1024,22 +1024,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-09-10 16:35:00</v>
+        <v>2026-09-09 16:35:00</v>
       </c>
       <c r="B30" t="str">
         <v>타행이체</v>
       </c>
       <c r="C30" t="str">
-        <v>우아한형제들</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D30" t="str">
         <v/>
       </c>
       <c r="E30">
-        <v>251600</v>
+        <v>400140</v>
       </c>
       <c r="F30">
-        <v>11099510</v>
+        <v>11158960</v>
       </c>
       <c r="G30" t="str">
         <v>가짜지점</v>
@@ -1047,22 +1047,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-09-10 17:46:00</v>
+        <v>2026-09-09 17:46:00</v>
       </c>
       <c r="B31" t="str">
         <v>타행이체</v>
       </c>
       <c r="C31" t="str">
-        <v>BC카드매출</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D31" t="str">
         <v/>
       </c>
       <c r="E31">
-        <v>442624</v>
+        <v>36270</v>
       </c>
       <c r="F31">
-        <v>11542134</v>
+        <v>11195230</v>
       </c>
       <c r="G31" t="str">
         <v>가짜지점</v>
@@ -1076,16 +1076,16 @@
         <v>타행이체</v>
       </c>
       <c r="C32" t="str">
-        <v>땡겨요정산</v>
+        <v>요기요정산</v>
       </c>
       <c r="D32" t="str">
         <v/>
       </c>
       <c r="E32">
-        <v>38130</v>
+        <v>67940</v>
       </c>
       <c r="F32">
-        <v>11580264</v>
+        <v>11263170</v>
       </c>
       <c r="G32" t="str">
         <v>가짜지점</v>
@@ -1096,19 +1096,19 @@
         <v>2026-09-10 10:08:00</v>
       </c>
       <c r="B33" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C33" t="str">
-        <v>가나식품</v>
-      </c>
-      <c r="D33">
-        <v>1450000</v>
-      </c>
-      <c r="E33" t="str">
-        <v/>
+        <v>쿠팡이츠정산</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33">
+        <v>632220</v>
       </c>
       <c r="F33">
-        <v>10130264</v>
+        <v>11895390</v>
       </c>
       <c r="G33" t="str">
         <v>가짜지점</v>
@@ -1119,19 +1119,19 @@
         <v>2026-09-10 11:19:00</v>
       </c>
       <c r="B34" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C34" t="str">
-        <v>급여(주방)</v>
-      </c>
-      <c r="D34">
-        <v>2800000</v>
-      </c>
-      <c r="E34" t="str">
-        <v/>
+        <v>우아한형제들</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34">
+        <v>251600</v>
       </c>
       <c r="F34">
-        <v>7330264</v>
+        <v>12146990</v>
       </c>
       <c r="G34" t="str">
         <v>가짜지점</v>
@@ -1139,22 +1139,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-09-11 12:30:00</v>
+        <v>2026-09-10 12:30:00</v>
       </c>
       <c r="B35" t="str">
         <v>타행이체</v>
       </c>
       <c r="C35" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D35" t="str">
         <v/>
       </c>
       <c r="E35">
-        <v>1077480</v>
+        <v>442624</v>
       </c>
       <c r="F35">
-        <v>8407744</v>
+        <v>12589614</v>
       </c>
       <c r="G35" t="str">
         <v>가짜지점</v>
@@ -1162,22 +1162,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-09-11 13:41:00</v>
+        <v>2026-09-10 13:41:00</v>
       </c>
       <c r="B36" t="str">
         <v>타행이체</v>
       </c>
       <c r="C36" t="str">
-        <v>요기요정산</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D36" t="str">
         <v/>
       </c>
       <c r="E36">
-        <v>284660</v>
+        <v>38130</v>
       </c>
       <c r="F36">
-        <v>8692404</v>
+        <v>12627744</v>
       </c>
       <c r="G36" t="str">
         <v>가짜지점</v>
@@ -1185,22 +1185,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-09-11 14:52:00</v>
+        <v>2026-09-10 14:52:00</v>
       </c>
       <c r="B37" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C37" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D37" t="str">
-        <v/>
-      </c>
-      <c r="E37">
-        <v>277950</v>
+        <v>가나식품</v>
+      </c>
+      <c r="D37">
+        <v>1450000</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
       </c>
       <c r="F37">
-        <v>8970354</v>
+        <v>11177744</v>
       </c>
       <c r="G37" t="str">
         <v>가짜지점</v>
@@ -1208,22 +1208,22 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-09-11 15:03:00</v>
+        <v>2026-09-10 15:03:00</v>
       </c>
       <c r="B38" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C38" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D38" t="str">
-        <v/>
-      </c>
-      <c r="E38">
-        <v>470288</v>
+        <v>급여(주방)</v>
+      </c>
+      <c r="D38">
+        <v>2800000</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
       </c>
       <c r="F38">
-        <v>9440642</v>
+        <v>8377744</v>
       </c>
       <c r="G38" t="str">
         <v>가짜지점</v>
@@ -1237,16 +1237,16 @@
         <v>타행이체</v>
       </c>
       <c r="C39" t="str">
-        <v>땡겨요정산</v>
+        <v>요기요정산</v>
       </c>
       <c r="D39" t="str">
         <v/>
       </c>
       <c r="E39">
-        <v>39060</v>
+        <v>284660</v>
       </c>
       <c r="F39">
-        <v>9479702</v>
+        <v>8662404</v>
       </c>
       <c r="G39" t="str">
         <v>가짜지점</v>
@@ -1254,22 +1254,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-09-14 17:25:00</v>
+        <v>2026-09-11 17:25:00</v>
       </c>
       <c r="B40" t="str">
         <v>타행이체</v>
       </c>
       <c r="C40" t="str">
-        <v>요기요정산</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D40" t="str">
         <v/>
       </c>
       <c r="E40">
-        <v>60200</v>
+        <v>133660</v>
       </c>
       <c r="F40">
-        <v>9539902</v>
+        <v>8796064</v>
       </c>
       <c r="G40" t="str">
         <v>가짜지점</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-09-14 09:36:00</v>
+        <v>2026-09-11 09:36:00</v>
       </c>
       <c r="B41" t="str">
         <v>타행이체</v>
@@ -1289,10 +1289,10 @@
         <v/>
       </c>
       <c r="E41">
-        <v>295800</v>
+        <v>277950</v>
       </c>
       <c r="F41">
-        <v>9835702</v>
+        <v>9074014</v>
       </c>
       <c r="G41" t="str">
         <v>가짜지점</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-09-14 10:47:00</v>
+        <v>2026-09-11 10:47:00</v>
       </c>
       <c r="B42" t="str">
         <v>타행이체</v>
@@ -1312,10 +1312,10 @@
         <v/>
       </c>
       <c r="E42">
-        <v>479180</v>
+        <v>470288</v>
       </c>
       <c r="F42">
-        <v>10314882</v>
+        <v>9544302</v>
       </c>
       <c r="G42" t="str">
         <v>가짜지점</v>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-09-14 11:58:00</v>
+        <v>2026-09-11 11:58:00</v>
       </c>
       <c r="B43" t="str">
         <v>타행이체</v>
@@ -1335,10 +1335,10 @@
         <v/>
       </c>
       <c r="E43">
-        <v>159960</v>
+        <v>39060</v>
       </c>
       <c r="F43">
-        <v>10474842</v>
+        <v>9583362</v>
       </c>
       <c r="G43" t="str">
         <v>가짜지점</v>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-09-15 12:09:00</v>
+        <v>2026-09-14 12:09:00</v>
       </c>
       <c r="B44" t="str">
         <v>타행이체</v>
@@ -1358,10 +1358,10 @@
         <v/>
       </c>
       <c r="E44">
-        <v>66220</v>
+        <v>60200</v>
       </c>
       <c r="F44">
-        <v>10541062</v>
+        <v>9643562</v>
       </c>
       <c r="G44" t="str">
         <v>가짜지점</v>
@@ -1369,22 +1369,22 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-09-15 13:20:00</v>
+        <v>2026-09-14 13:20:00</v>
       </c>
       <c r="B45" t="str">
         <v>타행이체</v>
       </c>
       <c r="C45" t="str">
-        <v>우아한형제들</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D45" t="str">
         <v/>
       </c>
       <c r="E45">
-        <v>301750</v>
+        <v>148420</v>
       </c>
       <c r="F45">
-        <v>10842812</v>
+        <v>9791982</v>
       </c>
       <c r="G45" t="str">
         <v>가짜지점</v>
@@ -1392,22 +1392,22 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-09-15 14:31:00</v>
+        <v>2026-09-14 14:31:00</v>
       </c>
       <c r="B46" t="str">
         <v>타행이체</v>
       </c>
       <c r="C46" t="str">
-        <v>BC카드매출</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D46" t="str">
         <v/>
       </c>
       <c r="E46">
-        <v>1957228</v>
+        <v>295800</v>
       </c>
       <c r="F46">
-        <v>12800040</v>
+        <v>10087782</v>
       </c>
       <c r="G46" t="str">
         <v>가짜지점</v>
@@ -1415,22 +1415,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-09-15 15:42:00</v>
+        <v>2026-09-14 15:42:00</v>
       </c>
       <c r="B47" t="str">
         <v>타행이체</v>
       </c>
       <c r="C47" t="str">
-        <v>땡겨요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D47" t="str">
         <v/>
       </c>
       <c r="E47">
-        <v>32550</v>
+        <v>479180</v>
       </c>
       <c r="F47">
-        <v>12832590</v>
+        <v>10566962</v>
       </c>
       <c r="G47" t="str">
         <v>가짜지점</v>
@@ -1438,22 +1438,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-09-15 16:53:00</v>
+        <v>2026-09-14 16:53:00</v>
       </c>
       <c r="B48" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C48" t="str">
-        <v>생활비이체</v>
-      </c>
-      <c r="D48">
-        <v>2500000</v>
-      </c>
-      <c r="E48" t="str">
-        <v/>
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48">
+        <v>159960</v>
       </c>
       <c r="F48">
-        <v>10332590</v>
+        <v>10726922</v>
       </c>
       <c r="G48" t="str">
         <v>가짜지점</v>
@@ -1461,7 +1461,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-09-16 17:04:00</v>
+        <v>2026-09-15 17:04:00</v>
       </c>
       <c r="B49" t="str">
         <v>타행이체</v>
@@ -1473,10 +1473,10 @@
         <v/>
       </c>
       <c r="E49">
-        <v>70520</v>
+        <v>66220</v>
       </c>
       <c r="F49">
-        <v>10403110</v>
+        <v>10793142</v>
       </c>
       <c r="G49" t="str">
         <v>가짜지점</v>
@@ -1484,22 +1484,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-09-16 09:15:00</v>
+        <v>2026-09-15 09:15:00</v>
       </c>
       <c r="B50" t="str">
         <v>타행이체</v>
       </c>
       <c r="C50" t="str">
-        <v>우아한형제들</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D50" t="str">
         <v/>
       </c>
       <c r="E50">
-        <v>1230800</v>
+        <v>157440</v>
       </c>
       <c r="F50">
-        <v>11633910</v>
+        <v>10950582</v>
       </c>
       <c r="G50" t="str">
         <v>가짜지점</v>
@@ -1507,22 +1507,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-09-16 10:26:00</v>
+        <v>2026-09-15 10:26:00</v>
       </c>
       <c r="B51" t="str">
         <v>타행이체</v>
       </c>
       <c r="C51" t="str">
-        <v>BC카드매출</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D51" t="str">
         <v/>
       </c>
       <c r="E51">
-        <v>400140</v>
+        <v>301750</v>
       </c>
       <c r="F51">
-        <v>12034050</v>
+        <v>11252332</v>
       </c>
       <c r="G51" t="str">
         <v>가짜지점</v>
@@ -1530,22 +1530,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-09-16 11:37:00</v>
+        <v>2026-09-15 11:37:00</v>
       </c>
       <c r="B52" t="str">
         <v>타행이체</v>
       </c>
       <c r="C52" t="str">
-        <v>땡겨요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D52" t="str">
         <v/>
       </c>
       <c r="E52">
-        <v>33480</v>
+        <v>1957228</v>
       </c>
       <c r="F52">
-        <v>12067530</v>
+        <v>13209560</v>
       </c>
       <c r="G52" t="str">
         <v>가짜지점</v>
@@ -1553,22 +1553,22 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-09-17 12:48:00</v>
+        <v>2026-09-15 12:48:00</v>
       </c>
       <c r="B53" t="str">
         <v>타행이체</v>
       </c>
       <c r="C53" t="str">
-        <v>요기요정산</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D53" t="str">
         <v/>
       </c>
       <c r="E53">
-        <v>72240</v>
+        <v>32550</v>
       </c>
       <c r="F53">
-        <v>12139770</v>
+        <v>13242110</v>
       </c>
       <c r="G53" t="str">
         <v>가짜지점</v>
@@ -1576,22 +1576,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-09-17 13:59:00</v>
+        <v>2026-09-15 13:59:00</v>
       </c>
       <c r="B54" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C54" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D54" t="str">
-        <v/>
-      </c>
-      <c r="E54">
-        <v>251600</v>
+        <v>생활비이체</v>
+      </c>
+      <c r="D54">
+        <v>2500000</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
       </c>
       <c r="F54">
-        <v>12391370</v>
+        <v>10742110</v>
       </c>
       <c r="G54" t="str">
         <v>가짜지점</v>
@@ -1599,22 +1599,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-09-17 14:10:00</v>
+        <v>2026-09-16 14:10:00</v>
       </c>
       <c r="B55" t="str">
         <v>타행이체</v>
       </c>
       <c r="C55" t="str">
-        <v>BC카드매출</v>
+        <v>요기요정산</v>
       </c>
       <c r="D55" t="str">
         <v/>
       </c>
       <c r="E55">
-        <v>411008</v>
+        <v>70520</v>
       </c>
       <c r="F55">
-        <v>12802378</v>
+        <v>10812630</v>
       </c>
       <c r="G55" t="str">
         <v>가짜지점</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-09-17 15:21:00</v>
+        <v>2026-09-16 15:21:00</v>
       </c>
       <c r="B56" t="str">
         <v>타행이체</v>
       </c>
       <c r="C56" t="str">
-        <v>땡겨요정산</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D56" t="str">
         <v/>
       </c>
       <c r="E56">
-        <v>35340</v>
+        <v>160720</v>
       </c>
       <c r="F56">
-        <v>12837718</v>
+        <v>10973350</v>
       </c>
       <c r="G56" t="str">
         <v>가짜지점</v>
@@ -1645,22 +1645,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-09-18 16:32:00</v>
+        <v>2026-09-16 16:32:00</v>
       </c>
       <c r="B57" t="str">
         <v>타행이체</v>
       </c>
       <c r="C57" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D57" t="str">
         <v/>
       </c>
       <c r="E57">
-        <v>1226240</v>
+        <v>1230800</v>
       </c>
       <c r="F57">
-        <v>14063958</v>
+        <v>12204150</v>
       </c>
       <c r="G57" t="str">
         <v>가짜지점</v>
@@ -1668,22 +1668,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-09-18 17:43:00</v>
+        <v>2026-09-16 17:43:00</v>
       </c>
       <c r="B58" t="str">
         <v>타행이체</v>
       </c>
       <c r="C58" t="str">
-        <v>요기요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D58" t="str">
         <v/>
       </c>
       <c r="E58">
-        <v>294980</v>
+        <v>400140</v>
       </c>
       <c r="F58">
-        <v>14358938</v>
+        <v>12604290</v>
       </c>
       <c r="G58" t="str">
         <v>가짜지점</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-09-18 09:54:00</v>
+        <v>2026-09-16 09:54:00</v>
       </c>
       <c r="B59" t="str">
         <v>타행이체</v>
       </c>
       <c r="C59" t="str">
-        <v>우아한형제들</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D59" t="str">
         <v/>
       </c>
       <c r="E59">
-        <v>258400</v>
+        <v>33480</v>
       </c>
       <c r="F59">
-        <v>14617338</v>
+        <v>12637770</v>
       </c>
       <c r="G59" t="str">
         <v>가짜지점</v>
@@ -1714,22 +1714,22 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-09-18 10:05:00</v>
+        <v>2026-09-17 10:05:00</v>
       </c>
       <c r="B60" t="str">
         <v>타행이체</v>
       </c>
       <c r="C60" t="str">
-        <v>BC카드매출</v>
+        <v>요기요정산</v>
       </c>
       <c r="D60" t="str">
         <v/>
       </c>
       <c r="E60">
-        <v>437684</v>
+        <v>72240</v>
       </c>
       <c r="F60">
-        <v>15055022</v>
+        <v>12710010</v>
       </c>
       <c r="G60" t="str">
         <v>가짜지점</v>
@@ -1737,30 +1737,214 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-09-18 11:16:00</v>
+        <v>2026-09-17 11:16:00</v>
       </c>
       <c r="B61" t="str">
         <v>타행이체</v>
       </c>
       <c r="C61" t="str">
+        <v>쿠팡이츠정산</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61">
+        <v>656000</v>
+      </c>
+      <c r="F61">
+        <v>13366010</v>
+      </c>
+      <c r="G61" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2026-09-17 12:27:00</v>
+      </c>
+      <c r="B62" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C62" t="str">
+        <v>우아한형제들</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62">
+        <v>251600</v>
+      </c>
+      <c r="F62">
+        <v>13617610</v>
+      </c>
+      <c r="G62" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2026-09-17 13:38:00</v>
+      </c>
+      <c r="B63" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C63" t="str">
+        <v>BC카드매출</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63">
+        <v>411008</v>
+      </c>
+      <c r="F63">
+        <v>14028618</v>
+      </c>
+      <c r="G63" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2026-09-17 14:49:00</v>
+      </c>
+      <c r="B64" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C64" t="str">
         <v>땡겨요정산</v>
       </c>
-      <c r="D61" t="str">
-        <v/>
-      </c>
-      <c r="E61">
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64">
+        <v>35340</v>
+      </c>
+      <c r="F64">
+        <v>14063958</v>
+      </c>
+      <c r="G64" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2026-09-18 15:00:00</v>
+      </c>
+      <c r="B65" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C65" t="str">
+        <v>요기요정산</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65">
+        <v>294980</v>
+      </c>
+      <c r="F65">
+        <v>14358938</v>
+      </c>
+      <c r="G65" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2026-09-18 16:11:00</v>
+      </c>
+      <c r="B66" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C66" t="str">
+        <v>쿠팡이츠정산</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66">
+        <v>133660</v>
+      </c>
+      <c r="F66">
+        <v>14492598</v>
+      </c>
+      <c r="G66" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2026-09-18 17:22:00</v>
+      </c>
+      <c r="B67" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C67" t="str">
+        <v>우아한형제들</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67">
+        <v>258400</v>
+      </c>
+      <c r="F67">
+        <v>14750998</v>
+      </c>
+      <c r="G67" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2026-09-18 09:33:00</v>
+      </c>
+      <c r="B68" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C68" t="str">
+        <v>BC카드매출</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68">
+        <v>437684</v>
+      </c>
+      <c r="F68">
+        <v>15188682</v>
+      </c>
+      <c r="G68" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2026-09-18 10:44:00</v>
+      </c>
+      <c r="B69" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C69" t="str">
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69">
         <v>40920</v>
       </c>
-      <c r="F61">
-        <v>15095942</v>
-      </c>
-      <c r="G61" t="str">
+      <c r="F69">
+        <v>15229602</v>
+      </c>
+      <c r="G69" t="str">
         <v>가짜지점</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/02_실전캠프_Day2_실습제출/3조_강상구_숯불에닭/v2/프로젝트/public/sample/가짜_거래내역_2026-09.xlsx
+++ b/02_실전캠프_Day2_실습제출/3조_강상구_숯불에닭/v2/프로젝트/public/sample/가짜_거래내역_2026-09.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G80"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -564,22 +564,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-09-03 14:55:00</v>
+        <v>2026-09-02 14:55:00</v>
       </c>
       <c r="B10" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C10" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10">
-        <v>410020</v>
+        <v>NH체크 가짜마트</v>
+      </c>
+      <c r="D10">
+        <v>48600</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
       </c>
       <c r="F10">
-        <v>8273500</v>
+        <v>7814880</v>
       </c>
       <c r="G10" t="str">
         <v>가짜지점</v>
@@ -593,16 +593,16 @@
         <v>타행이체</v>
       </c>
       <c r="C11" t="str">
-        <v>땡겨요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D11" t="str">
         <v/>
       </c>
       <c r="E11">
-        <v>38130</v>
+        <v>410020</v>
       </c>
       <c r="F11">
-        <v>8311630</v>
+        <v>8224900</v>
       </c>
       <c r="G11" t="str">
         <v>가짜지점</v>
@@ -613,19 +613,19 @@
         <v>2026-09-03 16:17:00</v>
       </c>
       <c r="B12" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C12" t="str">
-        <v>가나식품</v>
-      </c>
-      <c r="D12">
-        <v>1500000</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12">
+        <v>38130</v>
       </c>
       <c r="F12">
-        <v>6811630</v>
+        <v>8263030</v>
       </c>
       <c r="G12" t="str">
         <v>가짜지점</v>
@@ -633,22 +633,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-09-04 17:28:00</v>
+        <v>2026-09-03 17:28:00</v>
       </c>
       <c r="B13" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C13" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13">
-        <v>257550</v>
+        <v>가나식품</v>
+      </c>
+      <c r="D13">
+        <v>1500000</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
       </c>
       <c r="F13">
-        <v>7069180</v>
+        <v>6763030</v>
       </c>
       <c r="G13" t="str">
         <v>가짜지점</v>
@@ -662,16 +662,16 @@
         <v>타행이체</v>
       </c>
       <c r="C14" t="str">
-        <v>BC카드매출</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D14" t="str">
         <v/>
       </c>
       <c r="E14">
-        <v>468312</v>
+        <v>257550</v>
       </c>
       <c r="F14">
-        <v>7537492</v>
+        <v>7020580</v>
       </c>
       <c r="G14" t="str">
         <v>가짜지점</v>
@@ -685,16 +685,16 @@
         <v>타행이체</v>
       </c>
       <c r="C15" t="str">
-        <v>땡겨요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D15" t="str">
         <v/>
       </c>
       <c r="E15">
-        <v>36270</v>
+        <v>468312</v>
       </c>
       <c r="F15">
-        <v>7573762</v>
+        <v>7488892</v>
       </c>
       <c r="G15" t="str">
         <v>가짜지점</v>
@@ -702,22 +702,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-09-05 11:01:00</v>
+        <v>2026-09-04 11:01:00</v>
       </c>
       <c r="B16" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C16" t="str">
-        <v>숯닭본사(가맹)</v>
-      </c>
-      <c r="D16">
-        <v>1200000</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16">
+        <v>36270</v>
       </c>
       <c r="F16">
-        <v>6373762</v>
+        <v>7525162</v>
       </c>
       <c r="G16" t="str">
         <v>가짜지점</v>
@@ -725,22 +725,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-09-07 12:12:00</v>
+        <v>2026-09-04 12:12:00</v>
       </c>
       <c r="B17" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C17" t="str">
-        <v>쿠팡이츠정산</v>
-      </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17">
-        <v>137760</v>
+        <v>NH체크 가짜편의점</v>
+      </c>
+      <c r="D17">
+        <v>9600</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
       </c>
       <c r="F17">
-        <v>6511522</v>
+        <v>7515562</v>
       </c>
       <c r="G17" t="str">
         <v>가짜지점</v>
@@ -748,22 +748,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-09-07 13:23:00</v>
+        <v>2026-09-05 13:23:00</v>
       </c>
       <c r="B18" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C18" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18">
-        <v>294100</v>
+        <v>숯닭본사(가맹)</v>
+      </c>
+      <c r="D18">
+        <v>1200000</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
       </c>
       <c r="F18">
-        <v>6805622</v>
+        <v>6315562</v>
       </c>
       <c r="G18" t="str">
         <v>가짜지점</v>
@@ -771,22 +771,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-09-07 14:34:00</v>
+        <v>2026-09-06 14:34:00</v>
       </c>
       <c r="B19" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C19" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
-      <c r="E19">
-        <v>450528</v>
+        <v>NH체크 가짜마트</v>
+      </c>
+      <c r="D19">
+        <v>32400</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
       </c>
       <c r="F19">
-        <v>7256150</v>
+        <v>6283162</v>
       </c>
       <c r="G19" t="str">
         <v>가짜지점</v>
@@ -800,16 +800,16 @@
         <v>타행이체</v>
       </c>
       <c r="C20" t="str">
-        <v>땡겨요정산</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D20" t="str">
         <v/>
       </c>
       <c r="E20">
-        <v>153450</v>
+        <v>137760</v>
       </c>
       <c r="F20">
-        <v>7409600</v>
+        <v>6420922</v>
       </c>
       <c r="G20" t="str">
         <v>가짜지점</v>
@@ -817,22 +817,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-09-08 16:56:00</v>
+        <v>2026-09-07 16:56:00</v>
       </c>
       <c r="B21" t="str">
         <v>타행이체</v>
       </c>
       <c r="C21" t="str">
-        <v>요기요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D21" t="str">
         <v/>
       </c>
       <c r="E21">
-        <v>61920</v>
+        <v>294100</v>
       </c>
       <c r="F21">
-        <v>7471520</v>
+        <v>6715022</v>
       </c>
       <c r="G21" t="str">
         <v>가짜지점</v>
@@ -840,22 +840,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-09-08 17:07:00</v>
+        <v>2026-09-07 17:07:00</v>
       </c>
       <c r="B22" t="str">
         <v>타행이체</v>
       </c>
       <c r="C22" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D22" t="str">
         <v/>
       </c>
       <c r="E22">
-        <v>126620</v>
+        <v>450528</v>
       </c>
       <c r="F22">
-        <v>7598140</v>
+        <v>7165550</v>
       </c>
       <c r="G22" t="str">
         <v>가짜지점</v>
@@ -863,22 +863,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-09-08 09:18:00</v>
+        <v>2026-09-07 09:18:00</v>
       </c>
       <c r="B23" t="str">
         <v>타행이체</v>
       </c>
       <c r="C23" t="str">
-        <v>우아한형제들</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D23" t="str">
         <v/>
       </c>
       <c r="E23">
-        <v>283050</v>
+        <v>153450</v>
       </c>
       <c r="F23">
-        <v>7881190</v>
+        <v>7319000</v>
       </c>
       <c r="G23" t="str">
         <v>가짜지점</v>
@@ -892,16 +892,16 @@
         <v>타행이체</v>
       </c>
       <c r="C24" t="str">
-        <v>BC카드매출</v>
+        <v>요기요정산</v>
       </c>
       <c r="D24" t="str">
         <v/>
       </c>
       <c r="E24">
-        <v>1887080</v>
+        <v>61920</v>
       </c>
       <c r="F24">
-        <v>9768270</v>
+        <v>7380920</v>
       </c>
       <c r="G24" t="str">
         <v>가짜지점</v>
@@ -915,16 +915,16 @@
         <v>타행이체</v>
       </c>
       <c r="C25" t="str">
-        <v>땡겨요정산</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D25" t="str">
         <v/>
       </c>
       <c r="E25">
-        <v>32550</v>
+        <v>126620</v>
       </c>
       <c r="F25">
-        <v>9800820</v>
+        <v>7507540</v>
       </c>
       <c r="G25" t="str">
         <v>가짜지점</v>
@@ -935,19 +935,19 @@
         <v>2026-09-08 12:51:00</v>
       </c>
       <c r="B26" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C26" t="str">
-        <v>참숯나라</v>
-      </c>
-      <c r="D26">
-        <v>450000</v>
-      </c>
-      <c r="E26" t="str">
-        <v/>
+        <v>우아한형제들</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26">
+        <v>283050</v>
       </c>
       <c r="F26">
-        <v>9350820</v>
+        <v>7790590</v>
       </c>
       <c r="G26" t="str">
         <v>가짜지점</v>
@@ -955,22 +955,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-09-09 13:02:00</v>
+        <v>2026-09-08 13:02:00</v>
       </c>
       <c r="B27" t="str">
         <v>타행이체</v>
       </c>
       <c r="C27" t="str">
-        <v>요기요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D27" t="str">
         <v/>
       </c>
       <c r="E27">
-        <v>70520</v>
+        <v>1887080</v>
       </c>
       <c r="F27">
-        <v>9421340</v>
+        <v>9677670</v>
       </c>
       <c r="G27" t="str">
         <v>가짜지점</v>
@@ -978,22 +978,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-09-09 14:13:00</v>
+        <v>2026-09-08 14:13:00</v>
       </c>
       <c r="B28" t="str">
         <v>타행이체</v>
       </c>
       <c r="C28" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D28" t="str">
         <v/>
       </c>
       <c r="E28">
-        <v>150880</v>
+        <v>32550</v>
       </c>
       <c r="F28">
-        <v>9572220</v>
+        <v>9710220</v>
       </c>
       <c r="G28" t="str">
         <v>가짜지점</v>
@@ -1001,22 +1001,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-09-09 15:24:00</v>
+        <v>2026-09-08 15:24:00</v>
       </c>
       <c r="B29" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C29" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D29" t="str">
-        <v/>
-      </c>
-      <c r="E29">
-        <v>1186600</v>
+        <v>참숯나라</v>
+      </c>
+      <c r="D29">
+        <v>450000</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
       </c>
       <c r="F29">
-        <v>10758820</v>
+        <v>9260220</v>
       </c>
       <c r="G29" t="str">
         <v>가짜지점</v>
@@ -1024,22 +1024,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-09-09 16:35:00</v>
+        <v>2026-09-08 16:35:00</v>
       </c>
       <c r="B30" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C30" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D30" t="str">
-        <v/>
-      </c>
-      <c r="E30">
-        <v>400140</v>
+        <v>NH체크 가짜생활용품</v>
+      </c>
+      <c r="D30">
+        <v>16000</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
       </c>
       <c r="F30">
-        <v>11158960</v>
+        <v>9244220</v>
       </c>
       <c r="G30" t="str">
         <v>가짜지점</v>
@@ -1047,22 +1047,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-09-09 17:46:00</v>
+        <v>2026-09-08 17:46:00</v>
       </c>
       <c r="B31" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C31" t="str">
-        <v>땡겨요정산</v>
-      </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
-      <c r="E31">
-        <v>36270</v>
+        <v>NH체크 가짜생활용품</v>
+      </c>
+      <c r="D31">
+        <v>-16000</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
       </c>
       <c r="F31">
-        <v>11195230</v>
+        <v>9260220</v>
       </c>
       <c r="G31" t="str">
         <v>가짜지점</v>
@@ -1070,22 +1070,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-09-10 09:57:00</v>
+        <v>2026-09-08 09:57:00</v>
       </c>
       <c r="B32" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C32" t="str">
-        <v>요기요정산</v>
-      </c>
-      <c r="D32" t="str">
-        <v/>
-      </c>
-      <c r="E32">
-        <v>67940</v>
+        <v>NH체크 가짜생활용품</v>
+      </c>
+      <c r="D32">
+        <v>10000</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
       </c>
       <c r="F32">
-        <v>11263170</v>
+        <v>9250220</v>
       </c>
       <c r="G32" t="str">
         <v>가짜지점</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-09-10 10:08:00</v>
+        <v>2026-09-09 10:08:00</v>
       </c>
       <c r="B33" t="str">
         <v>타행이체</v>
       </c>
       <c r="C33" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>요기요정산</v>
       </c>
       <c r="D33" t="str">
         <v/>
       </c>
       <c r="E33">
-        <v>632220</v>
+        <v>70520</v>
       </c>
       <c r="F33">
-        <v>11895390</v>
+        <v>9320740</v>
       </c>
       <c r="G33" t="str">
         <v>가짜지점</v>
@@ -1116,22 +1116,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-09-10 11:19:00</v>
+        <v>2026-09-09 11:19:00</v>
       </c>
       <c r="B34" t="str">
         <v>타행이체</v>
       </c>
       <c r="C34" t="str">
-        <v>우아한형제들</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D34" t="str">
         <v/>
       </c>
       <c r="E34">
-        <v>251600</v>
+        <v>150880</v>
       </c>
       <c r="F34">
-        <v>12146990</v>
+        <v>9471620</v>
       </c>
       <c r="G34" t="str">
         <v>가짜지점</v>
@@ -1139,22 +1139,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-09-10 12:30:00</v>
+        <v>2026-09-09 12:30:00</v>
       </c>
       <c r="B35" t="str">
         <v>타행이체</v>
       </c>
       <c r="C35" t="str">
-        <v>BC카드매출</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D35" t="str">
         <v/>
       </c>
       <c r="E35">
-        <v>442624</v>
+        <v>1186600</v>
       </c>
       <c r="F35">
-        <v>12589614</v>
+        <v>10658220</v>
       </c>
       <c r="G35" t="str">
         <v>가짜지점</v>
@@ -1162,22 +1162,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-09-10 13:41:00</v>
+        <v>2026-09-09 13:41:00</v>
       </c>
       <c r="B36" t="str">
         <v>타행이체</v>
       </c>
       <c r="C36" t="str">
-        <v>땡겨요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D36" t="str">
         <v/>
       </c>
       <c r="E36">
-        <v>38130</v>
+        <v>400140</v>
       </c>
       <c r="F36">
-        <v>12627744</v>
+        <v>11058360</v>
       </c>
       <c r="G36" t="str">
         <v>가짜지점</v>
@@ -1185,22 +1185,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-09-10 14:52:00</v>
+        <v>2026-09-09 14:52:00</v>
       </c>
       <c r="B37" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C37" t="str">
-        <v>가나식품</v>
-      </c>
-      <c r="D37">
-        <v>1450000</v>
-      </c>
-      <c r="E37" t="str">
-        <v/>
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37">
+        <v>36270</v>
       </c>
       <c r="F37">
-        <v>11177744</v>
+        <v>11094630</v>
       </c>
       <c r="G37" t="str">
         <v>가짜지점</v>
@@ -1208,22 +1208,22 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-09-10 15:03:00</v>
+        <v>2026-09-09 15:03:00</v>
       </c>
       <c r="B38" t="str">
         <v>인터넷</v>
       </c>
       <c r="C38" t="str">
-        <v>급여(주방)</v>
+        <v>NH체크 네이버페이</v>
       </c>
       <c r="D38">
-        <v>2800000</v>
+        <v>76000</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38">
-        <v>8377744</v>
+        <v>11018630</v>
       </c>
       <c r="G38" t="str">
         <v>가짜지점</v>
@@ -1231,7 +1231,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-09-11 16:14:00</v>
+        <v>2026-09-10 16:14:00</v>
       </c>
       <c r="B39" t="str">
         <v>타행이체</v>
@@ -1243,10 +1243,10 @@
         <v/>
       </c>
       <c r="E39">
-        <v>284660</v>
+        <v>67940</v>
       </c>
       <c r="F39">
-        <v>8662404</v>
+        <v>11086570</v>
       </c>
       <c r="G39" t="str">
         <v>가짜지점</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-09-11 17:25:00</v>
+        <v>2026-09-10 17:25:00</v>
       </c>
       <c r="B40" t="str">
         <v>타행이체</v>
@@ -1266,10 +1266,10 @@
         <v/>
       </c>
       <c r="E40">
-        <v>133660</v>
+        <v>632220</v>
       </c>
       <c r="F40">
-        <v>8796064</v>
+        <v>11718790</v>
       </c>
       <c r="G40" t="str">
         <v>가짜지점</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-09-11 09:36:00</v>
+        <v>2026-09-10 09:36:00</v>
       </c>
       <c r="B41" t="str">
         <v>타행이체</v>
@@ -1289,10 +1289,10 @@
         <v/>
       </c>
       <c r="E41">
-        <v>277950</v>
+        <v>251600</v>
       </c>
       <c r="F41">
-        <v>9074014</v>
+        <v>11970390</v>
       </c>
       <c r="G41" t="str">
         <v>가짜지점</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-09-11 10:47:00</v>
+        <v>2026-09-10 10:47:00</v>
       </c>
       <c r="B42" t="str">
         <v>타행이체</v>
@@ -1312,10 +1312,10 @@
         <v/>
       </c>
       <c r="E42">
-        <v>470288</v>
+        <v>442624</v>
       </c>
       <c r="F42">
-        <v>9544302</v>
+        <v>12413014</v>
       </c>
       <c r="G42" t="str">
         <v>가짜지점</v>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-09-11 11:58:00</v>
+        <v>2026-09-10 11:58:00</v>
       </c>
       <c r="B43" t="str">
         <v>타행이체</v>
@@ -1335,10 +1335,10 @@
         <v/>
       </c>
       <c r="E43">
-        <v>39060</v>
+        <v>38130</v>
       </c>
       <c r="F43">
-        <v>9583362</v>
+        <v>12451144</v>
       </c>
       <c r="G43" t="str">
         <v>가짜지점</v>
@@ -1346,22 +1346,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-09-14 12:09:00</v>
+        <v>2026-09-10 12:09:00</v>
       </c>
       <c r="B44" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C44" t="str">
-        <v>요기요정산</v>
-      </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
-      <c r="E44">
-        <v>60200</v>
+        <v>가나식품</v>
+      </c>
+      <c r="D44">
+        <v>1450000</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
       </c>
       <c r="F44">
-        <v>9643562</v>
+        <v>11001144</v>
       </c>
       <c r="G44" t="str">
         <v>가짜지점</v>
@@ -1369,22 +1369,22 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-09-14 13:20:00</v>
+        <v>2026-09-10 13:20:00</v>
       </c>
       <c r="B45" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C45" t="str">
-        <v>쿠팡이츠정산</v>
-      </c>
-      <c r="D45" t="str">
-        <v/>
-      </c>
-      <c r="E45">
-        <v>148420</v>
+        <v>급여(주방)</v>
+      </c>
+      <c r="D45">
+        <v>2800000</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
       </c>
       <c r="F45">
-        <v>9791982</v>
+        <v>8201144</v>
       </c>
       <c r="G45" t="str">
         <v>가짜지점</v>
@@ -1392,22 +1392,22 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-09-14 14:31:00</v>
+        <v>2026-09-11 14:31:00</v>
       </c>
       <c r="B46" t="str">
         <v>타행이체</v>
       </c>
       <c r="C46" t="str">
-        <v>우아한형제들</v>
+        <v>요기요정산</v>
       </c>
       <c r="D46" t="str">
         <v/>
       </c>
       <c r="E46">
-        <v>295800</v>
+        <v>284660</v>
       </c>
       <c r="F46">
-        <v>10087782</v>
+        <v>8485804</v>
       </c>
       <c r="G46" t="str">
         <v>가짜지점</v>
@@ -1415,22 +1415,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-09-14 15:42:00</v>
+        <v>2026-09-11 15:42:00</v>
       </c>
       <c r="B47" t="str">
         <v>타행이체</v>
       </c>
       <c r="C47" t="str">
-        <v>BC카드매출</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D47" t="str">
         <v/>
       </c>
       <c r="E47">
-        <v>479180</v>
+        <v>133660</v>
       </c>
       <c r="F47">
-        <v>10566962</v>
+        <v>8619464</v>
       </c>
       <c r="G47" t="str">
         <v>가짜지점</v>
@@ -1438,22 +1438,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-09-14 16:53:00</v>
+        <v>2026-09-11 16:53:00</v>
       </c>
       <c r="B48" t="str">
         <v>타행이체</v>
       </c>
       <c r="C48" t="str">
-        <v>땡겨요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D48" t="str">
         <v/>
       </c>
       <c r="E48">
-        <v>159960</v>
+        <v>277950</v>
       </c>
       <c r="F48">
-        <v>10726922</v>
+        <v>8897414</v>
       </c>
       <c r="G48" t="str">
         <v>가짜지점</v>
@@ -1461,22 +1461,22 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-09-15 17:04:00</v>
+        <v>2026-09-11 17:04:00</v>
       </c>
       <c r="B49" t="str">
         <v>타행이체</v>
       </c>
       <c r="C49" t="str">
-        <v>요기요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D49" t="str">
         <v/>
       </c>
       <c r="E49">
-        <v>66220</v>
+        <v>470288</v>
       </c>
       <c r="F49">
-        <v>10793142</v>
+        <v>9367702</v>
       </c>
       <c r="G49" t="str">
         <v>가짜지점</v>
@@ -1484,22 +1484,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-09-15 09:15:00</v>
+        <v>2026-09-11 09:15:00</v>
       </c>
       <c r="B50" t="str">
         <v>타행이체</v>
       </c>
       <c r="C50" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D50" t="str">
         <v/>
       </c>
       <c r="E50">
-        <v>157440</v>
+        <v>39060</v>
       </c>
       <c r="F50">
-        <v>10950582</v>
+        <v>9406762</v>
       </c>
       <c r="G50" t="str">
         <v>가짜지점</v>
@@ -1507,22 +1507,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-09-15 10:26:00</v>
+        <v>2026-09-12 10:26:00</v>
       </c>
       <c r="B51" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C51" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D51" t="str">
-        <v/>
-      </c>
-      <c r="E51">
-        <v>301750</v>
+        <v>NH체크 (주)가짜유통</v>
+      </c>
+      <c r="D51">
+        <v>61800</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
       </c>
       <c r="F51">
-        <v>11252332</v>
+        <v>9344962</v>
       </c>
       <c r="G51" t="str">
         <v>가짜지점</v>
@@ -1530,22 +1530,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-09-15 11:37:00</v>
+        <v>2026-09-13 11:37:00</v>
       </c>
       <c r="B52" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C52" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D52" t="str">
-        <v/>
-      </c>
-      <c r="E52">
-        <v>1957228</v>
+        <v>NH체크 가짜철물</v>
+      </c>
+      <c r="D52">
+        <v>15000</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
       </c>
       <c r="F52">
-        <v>13209560</v>
+        <v>9329962</v>
       </c>
       <c r="G52" t="str">
         <v>가짜지점</v>
@@ -1553,22 +1553,22 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-09-15 12:48:00</v>
+        <v>2026-09-14 12:48:00</v>
       </c>
       <c r="B53" t="str">
         <v>타행이체</v>
       </c>
       <c r="C53" t="str">
-        <v>땡겨요정산</v>
+        <v>요기요정산</v>
       </c>
       <c r="D53" t="str">
         <v/>
       </c>
       <c r="E53">
-        <v>32550</v>
+        <v>60200</v>
       </c>
       <c r="F53">
-        <v>13242110</v>
+        <v>9390162</v>
       </c>
       <c r="G53" t="str">
         <v>가짜지점</v>
@@ -1576,22 +1576,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-09-15 13:59:00</v>
+        <v>2026-09-14 13:59:00</v>
       </c>
       <c r="B54" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C54" t="str">
-        <v>생활비이체</v>
-      </c>
-      <c r="D54">
-        <v>2500000</v>
-      </c>
-      <c r="E54" t="str">
-        <v/>
+        <v>쿠팡이츠정산</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54">
+        <v>148420</v>
       </c>
       <c r="F54">
-        <v>10742110</v>
+        <v>9538582</v>
       </c>
       <c r="G54" t="str">
         <v>가짜지점</v>
@@ -1599,22 +1599,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-09-16 14:10:00</v>
+        <v>2026-09-14 14:10:00</v>
       </c>
       <c r="B55" t="str">
         <v>타행이체</v>
       </c>
       <c r="C55" t="str">
-        <v>요기요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D55" t="str">
         <v/>
       </c>
       <c r="E55">
-        <v>70520</v>
+        <v>295800</v>
       </c>
       <c r="F55">
-        <v>10812630</v>
+        <v>9834382</v>
       </c>
       <c r="G55" t="str">
         <v>가짜지점</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-09-16 15:21:00</v>
+        <v>2026-09-14 15:21:00</v>
       </c>
       <c r="B56" t="str">
         <v>타행이체</v>
       </c>
       <c r="C56" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D56" t="str">
         <v/>
       </c>
       <c r="E56">
-        <v>160720</v>
+        <v>479180</v>
       </c>
       <c r="F56">
-        <v>10973350</v>
+        <v>10313562</v>
       </c>
       <c r="G56" t="str">
         <v>가짜지점</v>
@@ -1645,22 +1645,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-09-16 16:32:00</v>
+        <v>2026-09-14 16:32:00</v>
       </c>
       <c r="B57" t="str">
         <v>타행이체</v>
       </c>
       <c r="C57" t="str">
-        <v>우아한형제들</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D57" t="str">
         <v/>
       </c>
       <c r="E57">
-        <v>1230800</v>
+        <v>159960</v>
       </c>
       <c r="F57">
-        <v>12204150</v>
+        <v>10473522</v>
       </c>
       <c r="G57" t="str">
         <v>가짜지점</v>
@@ -1668,22 +1668,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-09-16 17:43:00</v>
+        <v>2026-09-15 17:43:00</v>
       </c>
       <c r="B58" t="str">
         <v>타행이체</v>
       </c>
       <c r="C58" t="str">
-        <v>BC카드매출</v>
+        <v>요기요정산</v>
       </c>
       <c r="D58" t="str">
         <v/>
       </c>
       <c r="E58">
-        <v>400140</v>
+        <v>66220</v>
       </c>
       <c r="F58">
-        <v>12604290</v>
+        <v>10539742</v>
       </c>
       <c r="G58" t="str">
         <v>가짜지점</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-09-16 09:54:00</v>
+        <v>2026-09-15 09:54:00</v>
       </c>
       <c r="B59" t="str">
         <v>타행이체</v>
       </c>
       <c r="C59" t="str">
-        <v>땡겨요정산</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D59" t="str">
         <v/>
       </c>
       <c r="E59">
-        <v>33480</v>
+        <v>157440</v>
       </c>
       <c r="F59">
-        <v>12637770</v>
+        <v>10697182</v>
       </c>
       <c r="G59" t="str">
         <v>가짜지점</v>
@@ -1714,22 +1714,22 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-09-17 10:05:00</v>
+        <v>2026-09-15 10:05:00</v>
       </c>
       <c r="B60" t="str">
         <v>타행이체</v>
       </c>
       <c r="C60" t="str">
-        <v>요기요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D60" t="str">
         <v/>
       </c>
       <c r="E60">
-        <v>72240</v>
+        <v>301750</v>
       </c>
       <c r="F60">
-        <v>12710010</v>
+        <v>10998932</v>
       </c>
       <c r="G60" t="str">
         <v>가짜지점</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-09-17 11:16:00</v>
+        <v>2026-09-15 11:16:00</v>
       </c>
       <c r="B61" t="str">
         <v>타행이체</v>
       </c>
       <c r="C61" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D61" t="str">
         <v/>
       </c>
       <c r="E61">
-        <v>656000</v>
+        <v>1957228</v>
       </c>
       <c r="F61">
-        <v>13366010</v>
+        <v>12956160</v>
       </c>
       <c r="G61" t="str">
         <v>가짜지점</v>
@@ -1760,22 +1760,22 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-09-17 12:27:00</v>
+        <v>2026-09-15 12:27:00</v>
       </c>
       <c r="B62" t="str">
         <v>타행이체</v>
       </c>
       <c r="C62" t="str">
-        <v>우아한형제들</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D62" t="str">
         <v/>
       </c>
       <c r="E62">
-        <v>251600</v>
+        <v>32550</v>
       </c>
       <c r="F62">
-        <v>13617610</v>
+        <v>12988710</v>
       </c>
       <c r="G62" t="str">
         <v>가짜지점</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-09-17 13:38:00</v>
+        <v>2026-09-15 13:38:00</v>
       </c>
       <c r="B63" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C63" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D63" t="str">
-        <v/>
-      </c>
-      <c r="E63">
-        <v>411008</v>
+        <v>생활비이체</v>
+      </c>
+      <c r="D63">
+        <v>2500000</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
       </c>
       <c r="F63">
-        <v>14028618</v>
+        <v>10488710</v>
       </c>
       <c r="G63" t="str">
         <v>가짜지점</v>
@@ -1806,22 +1806,22 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-09-17 14:49:00</v>
+        <v>2026-09-15 14:49:00</v>
       </c>
       <c r="B64" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C64" t="str">
-        <v>땡겨요정산</v>
-      </c>
-      <c r="D64" t="str">
-        <v/>
-      </c>
-      <c r="E64">
-        <v>35340</v>
+        <v>NH체크 가짜마트</v>
+      </c>
+      <c r="D64">
+        <v>27900</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
       </c>
       <c r="F64">
-        <v>14063958</v>
+        <v>10460810</v>
       </c>
       <c r="G64" t="str">
         <v>가짜지점</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-09-18 15:00:00</v>
+        <v>2026-09-16 15:00:00</v>
       </c>
       <c r="B65" t="str">
         <v>타행이체</v>
@@ -1841,10 +1841,10 @@
         <v/>
       </c>
       <c r="E65">
-        <v>294980</v>
+        <v>70520</v>
       </c>
       <c r="F65">
-        <v>14358938</v>
+        <v>10531330</v>
       </c>
       <c r="G65" t="str">
         <v>가짜지점</v>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-09-18 16:11:00</v>
+        <v>2026-09-16 16:11:00</v>
       </c>
       <c r="B66" t="str">
         <v>타행이체</v>
@@ -1864,10 +1864,10 @@
         <v/>
       </c>
       <c r="E66">
-        <v>133660</v>
+        <v>160720</v>
       </c>
       <c r="F66">
-        <v>14492598</v>
+        <v>10692050</v>
       </c>
       <c r="G66" t="str">
         <v>가짜지점</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-09-18 17:22:00</v>
+        <v>2026-09-16 17:22:00</v>
       </c>
       <c r="B67" t="str">
         <v>타행이체</v>
@@ -1887,10 +1887,10 @@
         <v/>
       </c>
       <c r="E67">
-        <v>258400</v>
+        <v>1230800</v>
       </c>
       <c r="F67">
-        <v>14750998</v>
+        <v>11922850</v>
       </c>
       <c r="G67" t="str">
         <v>가짜지점</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-09-18 09:33:00</v>
+        <v>2026-09-16 09:33:00</v>
       </c>
       <c r="B68" t="str">
         <v>타행이체</v>
@@ -1910,10 +1910,10 @@
         <v/>
       </c>
       <c r="E68">
-        <v>437684</v>
+        <v>400140</v>
       </c>
       <c r="F68">
-        <v>15188682</v>
+        <v>12322990</v>
       </c>
       <c r="G68" t="str">
         <v>가짜지점</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-09-18 10:44:00</v>
+        <v>2026-09-16 10:44:00</v>
       </c>
       <c r="B69" t="str">
         <v>타행이체</v>
@@ -1933,18 +1933,271 @@
         <v/>
       </c>
       <c r="E69">
+        <v>33480</v>
+      </c>
+      <c r="F69">
+        <v>12356470</v>
+      </c>
+      <c r="G69" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2026-09-16 11:55:00</v>
+      </c>
+      <c r="B70" t="str">
+        <v>인터넷</v>
+      </c>
+      <c r="C70" t="str">
+        <v>NH체크 가짜주차</v>
+      </c>
+      <c r="D70">
+        <v>7000</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70">
+        <v>12349470</v>
+      </c>
+      <c r="G70" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2026-09-17 12:06:00</v>
+      </c>
+      <c r="B71" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C71" t="str">
+        <v>요기요정산</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71">
+        <v>72240</v>
+      </c>
+      <c r="F71">
+        <v>12421710</v>
+      </c>
+      <c r="G71" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2026-09-17 13:17:00</v>
+      </c>
+      <c r="B72" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C72" t="str">
+        <v>쿠팡이츠정산</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72">
+        <v>656000</v>
+      </c>
+      <c r="F72">
+        <v>13077710</v>
+      </c>
+      <c r="G72" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2026-09-17 14:28:00</v>
+      </c>
+      <c r="B73" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C73" t="str">
+        <v>우아한형제들</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73">
+        <v>251600</v>
+      </c>
+      <c r="F73">
+        <v>13329310</v>
+      </c>
+      <c r="G73" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2026-09-17 15:39:00</v>
+      </c>
+      <c r="B74" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C74" t="str">
+        <v>BC카드매출</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74">
+        <v>411008</v>
+      </c>
+      <c r="F74">
+        <v>13740318</v>
+      </c>
+      <c r="G74" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2026-09-17 16:50:00</v>
+      </c>
+      <c r="B75" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C75" t="str">
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75">
+        <v>35340</v>
+      </c>
+      <c r="F75">
+        <v>13775658</v>
+      </c>
+      <c r="G75" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2026-09-18 17:01:00</v>
+      </c>
+      <c r="B76" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C76" t="str">
+        <v>요기요정산</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76">
+        <v>294980</v>
+      </c>
+      <c r="F76">
+        <v>14070638</v>
+      </c>
+      <c r="G76" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2026-09-18 09:12:00</v>
+      </c>
+      <c r="B77" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C77" t="str">
+        <v>쿠팡이츠정산</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77">
+        <v>133660</v>
+      </c>
+      <c r="F77">
+        <v>14204298</v>
+      </c>
+      <c r="G77" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2026-09-18 10:23:00</v>
+      </c>
+      <c r="B78" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C78" t="str">
+        <v>우아한형제들</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78">
+        <v>258400</v>
+      </c>
+      <c r="F78">
+        <v>14462698</v>
+      </c>
+      <c r="G78" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2026-09-18 11:34:00</v>
+      </c>
+      <c r="B79" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C79" t="str">
+        <v>BC카드매출</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79">
+        <v>437684</v>
+      </c>
+      <c r="F79">
+        <v>14900382</v>
+      </c>
+      <c r="G79" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2026-09-18 12:45:00</v>
+      </c>
+      <c r="B80" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C80" t="str">
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80">
         <v>40920</v>
       </c>
-      <c r="F69">
-        <v>15229602</v>
-      </c>
-      <c r="G69" t="str">
+      <c r="F80">
+        <v>14941302</v>
+      </c>
+      <c r="G80" t="str">
         <v>가짜지점</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G80"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/02_실전캠프_Day2_실습제출/3조_강상구_숯불에닭/v2/프로젝트/public/sample/가짜_거래내역_2026-09.xlsx
+++ b/02_실전캠프_Day2_실습제출/3조_강상구_숯불에닭/v2/프로젝트/public/sample/가짜_거래내역_2026-09.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G93"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -731,16 +731,16 @@
         <v>인터넷</v>
       </c>
       <c r="C17" t="str">
-        <v>NH체크 가짜편의점</v>
+        <v>가나식품</v>
       </c>
       <c r="D17">
-        <v>9600</v>
+        <v>1550000</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17">
-        <v>7515562</v>
+        <v>5975162</v>
       </c>
       <c r="G17" t="str">
         <v>가짜지점</v>
@@ -748,22 +748,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-09-05 13:23:00</v>
+        <v>2026-09-04 13:23:00</v>
       </c>
       <c r="B18" t="str">
         <v>인터넷</v>
       </c>
       <c r="C18" t="str">
-        <v>숯닭본사(가맹)</v>
+        <v>NH체크 가짜편의점</v>
       </c>
       <c r="D18">
-        <v>1200000</v>
+        <v>9600</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18">
-        <v>6315562</v>
+        <v>5965562</v>
       </c>
       <c r="G18" t="str">
         <v>가짜지점</v>
@@ -771,22 +771,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-09-06 14:34:00</v>
+        <v>2026-09-05 14:34:00</v>
       </c>
       <c r="B19" t="str">
         <v>인터넷</v>
       </c>
       <c r="C19" t="str">
-        <v>NH체크 가짜마트</v>
+        <v>숯닭본사(가맹)</v>
       </c>
       <c r="D19">
-        <v>32400</v>
+        <v>1200000</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19">
-        <v>6283162</v>
+        <v>4765562</v>
       </c>
       <c r="G19" t="str">
         <v>가짜지점</v>
@@ -794,22 +794,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-09-07 15:45:00</v>
+        <v>2026-09-05 15:45:00</v>
       </c>
       <c r="B20" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C20" t="str">
-        <v>쿠팡이츠정산</v>
-      </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20">
-        <v>137760</v>
+        <v>새벽채소</v>
+      </c>
+      <c r="D20">
+        <v>310000</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
       </c>
       <c r="F20">
-        <v>6420922</v>
+        <v>4455562</v>
       </c>
       <c r="G20" t="str">
         <v>가짜지점</v>
@@ -817,22 +817,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-09-07 16:56:00</v>
+        <v>2026-09-06 16:56:00</v>
       </c>
       <c r="B21" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C21" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21">
-        <v>294100</v>
+        <v>다라유통</v>
+      </c>
+      <c r="D21">
+        <v>890000</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
       </c>
       <c r="F21">
-        <v>6715022</v>
+        <v>3565562</v>
       </c>
       <c r="G21" t="str">
         <v>가짜지점</v>
@@ -840,22 +840,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-09-07 17:07:00</v>
+        <v>2026-09-06 17:07:00</v>
       </c>
       <c r="B22" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C22" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22">
-        <v>450528</v>
+        <v>NH체크 가짜마트</v>
+      </c>
+      <c r="D22">
+        <v>32400</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
       </c>
       <c r="F22">
-        <v>7165550</v>
+        <v>3533162</v>
       </c>
       <c r="G22" t="str">
         <v>가짜지점</v>
@@ -869,16 +869,16 @@
         <v>타행이체</v>
       </c>
       <c r="C23" t="str">
-        <v>땡겨요정산</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D23" t="str">
         <v/>
       </c>
       <c r="E23">
-        <v>153450</v>
+        <v>137760</v>
       </c>
       <c r="F23">
-        <v>7319000</v>
+        <v>3670922</v>
       </c>
       <c r="G23" t="str">
         <v>가짜지점</v>
@@ -886,22 +886,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-09-08 10:29:00</v>
+        <v>2026-09-07 10:29:00</v>
       </c>
       <c r="B24" t="str">
         <v>타행이체</v>
       </c>
       <c r="C24" t="str">
-        <v>요기요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D24" t="str">
         <v/>
       </c>
       <c r="E24">
-        <v>61920</v>
+        <v>294100</v>
       </c>
       <c r="F24">
-        <v>7380920</v>
+        <v>3965022</v>
       </c>
       <c r="G24" t="str">
         <v>가짜지점</v>
@@ -909,22 +909,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-09-08 11:40:00</v>
+        <v>2026-09-07 11:40:00</v>
       </c>
       <c r="B25" t="str">
         <v>타행이체</v>
       </c>
       <c r="C25" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D25" t="str">
         <v/>
       </c>
       <c r="E25">
-        <v>126620</v>
+        <v>450528</v>
       </c>
       <c r="F25">
-        <v>7507540</v>
+        <v>4415550</v>
       </c>
       <c r="G25" t="str">
         <v>가짜지점</v>
@@ -932,22 +932,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-09-08 12:51:00</v>
+        <v>2026-09-07 12:51:00</v>
       </c>
       <c r="B26" t="str">
         <v>타행이체</v>
       </c>
       <c r="C26" t="str">
-        <v>우아한형제들</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D26" t="str">
         <v/>
       </c>
       <c r="E26">
-        <v>283050</v>
+        <v>153450</v>
       </c>
       <c r="F26">
-        <v>7790590</v>
+        <v>4569000</v>
       </c>
       <c r="G26" t="str">
         <v>가짜지점</v>
@@ -961,16 +961,16 @@
         <v>타행이체</v>
       </c>
       <c r="C27" t="str">
-        <v>BC카드매출</v>
+        <v>요기요정산</v>
       </c>
       <c r="D27" t="str">
         <v/>
       </c>
       <c r="E27">
-        <v>1887080</v>
+        <v>61920</v>
       </c>
       <c r="F27">
-        <v>9677670</v>
+        <v>4630920</v>
       </c>
       <c r="G27" t="str">
         <v>가짜지점</v>
@@ -984,16 +984,16 @@
         <v>타행이체</v>
       </c>
       <c r="C28" t="str">
-        <v>땡겨요정산</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D28" t="str">
         <v/>
       </c>
       <c r="E28">
-        <v>32550</v>
+        <v>126620</v>
       </c>
       <c r="F28">
-        <v>9710220</v>
+        <v>4757540</v>
       </c>
       <c r="G28" t="str">
         <v>가짜지점</v>
@@ -1004,19 +1004,19 @@
         <v>2026-09-08 15:24:00</v>
       </c>
       <c r="B29" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C29" t="str">
-        <v>참숯나라</v>
-      </c>
-      <c r="D29">
-        <v>450000</v>
-      </c>
-      <c r="E29" t="str">
-        <v/>
+        <v>우아한형제들</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29">
+        <v>283050</v>
       </c>
       <c r="F29">
-        <v>9260220</v>
+        <v>5040590</v>
       </c>
       <c r="G29" t="str">
         <v>가짜지점</v>
@@ -1027,19 +1027,19 @@
         <v>2026-09-08 16:35:00</v>
       </c>
       <c r="B30" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C30" t="str">
-        <v>NH체크 가짜생활용품</v>
-      </c>
-      <c r="D30">
-        <v>16000</v>
-      </c>
-      <c r="E30" t="str">
-        <v/>
+        <v>BC카드매출</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30">
+        <v>1887080</v>
       </c>
       <c r="F30">
-        <v>9244220</v>
+        <v>6927670</v>
       </c>
       <c r="G30" t="str">
         <v>가짜지점</v>
@@ -1050,19 +1050,19 @@
         <v>2026-09-08 17:46:00</v>
       </c>
       <c r="B31" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C31" t="str">
-        <v>NH체크 가짜생활용품</v>
-      </c>
-      <c r="D31">
-        <v>-16000</v>
-      </c>
-      <c r="E31" t="str">
-        <v/>
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31">
+        <v>32550</v>
       </c>
       <c r="F31">
-        <v>9260220</v>
+        <v>6960220</v>
       </c>
       <c r="G31" t="str">
         <v>가짜지점</v>
@@ -1076,16 +1076,16 @@
         <v>인터넷</v>
       </c>
       <c r="C32" t="str">
-        <v>NH체크 가짜생활용품</v>
+        <v>참숯나라</v>
       </c>
       <c r="D32">
-        <v>10000</v>
+        <v>450000</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32">
-        <v>9250220</v>
+        <v>6510220</v>
       </c>
       <c r="G32" t="str">
         <v>가짜지점</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-09-09 10:08:00</v>
+        <v>2026-09-08 10:08:00</v>
       </c>
       <c r="B33" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C33" t="str">
-        <v>요기요정산</v>
-      </c>
-      <c r="D33" t="str">
-        <v/>
-      </c>
-      <c r="E33">
-        <v>70520</v>
+        <v>바로고 배달대행</v>
+      </c>
+      <c r="D33">
+        <v>1000000</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
       </c>
       <c r="F33">
-        <v>9320740</v>
+        <v>5510220</v>
       </c>
       <c r="G33" t="str">
         <v>가짜지점</v>
@@ -1116,22 +1116,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-09-09 11:19:00</v>
+        <v>2026-09-08 11:19:00</v>
       </c>
       <c r="B34" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C34" t="str">
-        <v>쿠팡이츠정산</v>
-      </c>
-      <c r="D34" t="str">
-        <v/>
-      </c>
-      <c r="E34">
-        <v>150880</v>
+        <v>NH체크 가짜생활용품</v>
+      </c>
+      <c r="D34">
+        <v>16000</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
       </c>
       <c r="F34">
-        <v>9471620</v>
+        <v>5494220</v>
       </c>
       <c r="G34" t="str">
         <v>가짜지점</v>
@@ -1139,22 +1139,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-09-09 12:30:00</v>
+        <v>2026-09-08 12:30:00</v>
       </c>
       <c r="B35" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C35" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D35" t="str">
-        <v/>
-      </c>
-      <c r="E35">
-        <v>1186600</v>
+        <v>NH체크 가짜생활용품</v>
+      </c>
+      <c r="D35">
+        <v>-16000</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
       </c>
       <c r="F35">
-        <v>10658220</v>
+        <v>5510220</v>
       </c>
       <c r="G35" t="str">
         <v>가짜지점</v>
@@ -1162,22 +1162,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-09-09 13:41:00</v>
+        <v>2026-09-08 13:41:00</v>
       </c>
       <c r="B36" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C36" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D36" t="str">
-        <v/>
-      </c>
-      <c r="E36">
-        <v>400140</v>
+        <v>NH체크 가짜생활용품</v>
+      </c>
+      <c r="D36">
+        <v>10000</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
       </c>
       <c r="F36">
-        <v>11058360</v>
+        <v>5500220</v>
       </c>
       <c r="G36" t="str">
         <v>가짜지점</v>
@@ -1191,16 +1191,16 @@
         <v>타행이체</v>
       </c>
       <c r="C37" t="str">
-        <v>땡겨요정산</v>
+        <v>요기요정산</v>
       </c>
       <c r="D37" t="str">
         <v/>
       </c>
       <c r="E37">
-        <v>36270</v>
+        <v>70520</v>
       </c>
       <c r="F37">
-        <v>11094630</v>
+        <v>5570740</v>
       </c>
       <c r="G37" t="str">
         <v>가짜지점</v>
@@ -1211,19 +1211,19 @@
         <v>2026-09-09 15:03:00</v>
       </c>
       <c r="B38" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C38" t="str">
-        <v>NH체크 네이버페이</v>
-      </c>
-      <c r="D38">
-        <v>76000</v>
-      </c>
-      <c r="E38" t="str">
-        <v/>
+        <v>쿠팡이츠정산</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38">
+        <v>150880</v>
       </c>
       <c r="F38">
-        <v>11018630</v>
+        <v>5721620</v>
       </c>
       <c r="G38" t="str">
         <v>가짜지점</v>
@@ -1231,22 +1231,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-09-10 16:14:00</v>
+        <v>2026-09-09 16:14:00</v>
       </c>
       <c r="B39" t="str">
         <v>타행이체</v>
       </c>
       <c r="C39" t="str">
-        <v>요기요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D39" t="str">
         <v/>
       </c>
       <c r="E39">
-        <v>67940</v>
+        <v>1186600</v>
       </c>
       <c r="F39">
-        <v>11086570</v>
+        <v>6908220</v>
       </c>
       <c r="G39" t="str">
         <v>가짜지점</v>
@@ -1254,22 +1254,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-09-10 17:25:00</v>
+        <v>2026-09-09 17:25:00</v>
       </c>
       <c r="B40" t="str">
         <v>타행이체</v>
       </c>
       <c r="C40" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D40" t="str">
         <v/>
       </c>
       <c r="E40">
-        <v>632220</v>
+        <v>400140</v>
       </c>
       <c r="F40">
-        <v>11718790</v>
+        <v>7308360</v>
       </c>
       <c r="G40" t="str">
         <v>가짜지점</v>
@@ -1277,22 +1277,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-09-10 09:36:00</v>
+        <v>2026-09-09 09:36:00</v>
       </c>
       <c r="B41" t="str">
         <v>타행이체</v>
       </c>
       <c r="C41" t="str">
-        <v>우아한형제들</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D41" t="str">
         <v/>
       </c>
       <c r="E41">
-        <v>251600</v>
+        <v>36270</v>
       </c>
       <c r="F41">
-        <v>11970390</v>
+        <v>7344630</v>
       </c>
       <c r="G41" t="str">
         <v>가짜지점</v>
@@ -1300,22 +1300,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-09-10 10:47:00</v>
+        <v>2026-09-09 10:47:00</v>
       </c>
       <c r="B42" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C42" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D42" t="str">
-        <v/>
-      </c>
-      <c r="E42">
-        <v>442624</v>
+        <v>NH체크 네이버페이</v>
+      </c>
+      <c r="D42">
+        <v>76000</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
       </c>
       <c r="F42">
-        <v>12413014</v>
+        <v>7268630</v>
       </c>
       <c r="G42" t="str">
         <v>가짜지점</v>
@@ -1329,16 +1329,16 @@
         <v>타행이체</v>
       </c>
       <c r="C43" t="str">
-        <v>땡겨요정산</v>
+        <v>요기요정산</v>
       </c>
       <c r="D43" t="str">
         <v/>
       </c>
       <c r="E43">
-        <v>38130</v>
+        <v>67940</v>
       </c>
       <c r="F43">
-        <v>12451144</v>
+        <v>7336570</v>
       </c>
       <c r="G43" t="str">
         <v>가짜지점</v>
@@ -1349,19 +1349,19 @@
         <v>2026-09-10 12:09:00</v>
       </c>
       <c r="B44" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C44" t="str">
-        <v>가나식품</v>
-      </c>
-      <c r="D44">
-        <v>1450000</v>
-      </c>
-      <c r="E44" t="str">
-        <v/>
+        <v>쿠팡이츠정산</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44">
+        <v>632220</v>
       </c>
       <c r="F44">
-        <v>11001144</v>
+        <v>7968790</v>
       </c>
       <c r="G44" t="str">
         <v>가짜지점</v>
@@ -1372,19 +1372,19 @@
         <v>2026-09-10 13:20:00</v>
       </c>
       <c r="B45" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C45" t="str">
-        <v>급여(주방)</v>
-      </c>
-      <c r="D45">
-        <v>2800000</v>
-      </c>
-      <c r="E45" t="str">
-        <v/>
+        <v>우아한형제들</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45">
+        <v>251600</v>
       </c>
       <c r="F45">
-        <v>8201144</v>
+        <v>8220390</v>
       </c>
       <c r="G45" t="str">
         <v>가짜지점</v>
@@ -1392,22 +1392,22 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-09-11 14:31:00</v>
+        <v>2026-09-10 14:31:00</v>
       </c>
       <c r="B46" t="str">
         <v>타행이체</v>
       </c>
       <c r="C46" t="str">
-        <v>요기요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D46" t="str">
         <v/>
       </c>
       <c r="E46">
-        <v>284660</v>
+        <v>442624</v>
       </c>
       <c r="F46">
-        <v>8485804</v>
+        <v>8663014</v>
       </c>
       <c r="G46" t="str">
         <v>가짜지점</v>
@@ -1415,22 +1415,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-09-11 15:42:00</v>
+        <v>2026-09-10 15:42:00</v>
       </c>
       <c r="B47" t="str">
         <v>타행이체</v>
       </c>
       <c r="C47" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D47" t="str">
         <v/>
       </c>
       <c r="E47">
-        <v>133660</v>
+        <v>38130</v>
       </c>
       <c r="F47">
-        <v>8619464</v>
+        <v>8701144</v>
       </c>
       <c r="G47" t="str">
         <v>가짜지점</v>
@@ -1438,22 +1438,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-09-11 16:53:00</v>
+        <v>2026-09-10 16:53:00</v>
       </c>
       <c r="B48" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C48" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D48" t="str">
-        <v/>
-      </c>
-      <c r="E48">
-        <v>277950</v>
+        <v>가나식품</v>
+      </c>
+      <c r="D48">
+        <v>1450000</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
       </c>
       <c r="F48">
-        <v>8897414</v>
+        <v>7251144</v>
       </c>
       <c r="G48" t="str">
         <v>가짜지점</v>
@@ -1461,22 +1461,22 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-09-11 17:04:00</v>
+        <v>2026-09-10 17:04:00</v>
       </c>
       <c r="B49" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C49" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D49" t="str">
-        <v/>
-      </c>
-      <c r="E49">
-        <v>470288</v>
+        <v>급여(주방)</v>
+      </c>
+      <c r="D49">
+        <v>2800000</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
       </c>
       <c r="F49">
-        <v>9367702</v>
+        <v>4451144</v>
       </c>
       <c r="G49" t="str">
         <v>가짜지점</v>
@@ -1484,22 +1484,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-09-11 09:15:00</v>
+        <v>2026-09-10 09:15:00</v>
       </c>
       <c r="B50" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C50" t="str">
-        <v>땡겨요정산</v>
-      </c>
-      <c r="D50" t="str">
-        <v/>
-      </c>
-      <c r="E50">
-        <v>39060</v>
+        <v>부가세(예정고지)</v>
+      </c>
+      <c r="D50">
+        <v>800000</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
       </c>
       <c r="F50">
-        <v>9406762</v>
+        <v>3651144</v>
       </c>
       <c r="G50" t="str">
         <v>가짜지점</v>
@@ -1507,22 +1507,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-09-12 10:26:00</v>
+        <v>2026-09-10 10:26:00</v>
       </c>
       <c r="B51" t="str">
         <v>인터넷</v>
       </c>
       <c r="C51" t="str">
-        <v>NH체크 (주)가짜유통</v>
+        <v>지방소득세</v>
       </c>
       <c r="D51">
-        <v>61800</v>
+        <v>120000</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51">
-        <v>9344962</v>
+        <v>3531144</v>
       </c>
       <c r="G51" t="str">
         <v>가짜지점</v>
@@ -1530,22 +1530,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-09-13 11:37:00</v>
+        <v>2026-09-11 11:37:00</v>
       </c>
       <c r="B52" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C52" t="str">
-        <v>NH체크 가짜철물</v>
-      </c>
-      <c r="D52">
-        <v>15000</v>
-      </c>
-      <c r="E52" t="str">
-        <v/>
+        <v>요기요정산</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52">
+        <v>284660</v>
       </c>
       <c r="F52">
-        <v>9329962</v>
+        <v>3815804</v>
       </c>
       <c r="G52" t="str">
         <v>가짜지점</v>
@@ -1553,22 +1553,22 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-09-14 12:48:00</v>
+        <v>2026-09-11 12:48:00</v>
       </c>
       <c r="B53" t="str">
         <v>타행이체</v>
       </c>
       <c r="C53" t="str">
-        <v>요기요정산</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D53" t="str">
         <v/>
       </c>
       <c r="E53">
-        <v>60200</v>
+        <v>133660</v>
       </c>
       <c r="F53">
-        <v>9390162</v>
+        <v>3949464</v>
       </c>
       <c r="G53" t="str">
         <v>가짜지점</v>
@@ -1576,22 +1576,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-09-14 13:59:00</v>
+        <v>2026-09-11 13:59:00</v>
       </c>
       <c r="B54" t="str">
         <v>타행이체</v>
       </c>
       <c r="C54" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D54" t="str">
         <v/>
       </c>
       <c r="E54">
-        <v>148420</v>
+        <v>277950</v>
       </c>
       <c r="F54">
-        <v>9538582</v>
+        <v>4227414</v>
       </c>
       <c r="G54" t="str">
         <v>가짜지점</v>
@@ -1599,22 +1599,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-09-14 14:10:00</v>
+        <v>2026-09-11 14:10:00</v>
       </c>
       <c r="B55" t="str">
         <v>타행이체</v>
       </c>
       <c r="C55" t="str">
-        <v>우아한형제들</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D55" t="str">
         <v/>
       </c>
       <c r="E55">
-        <v>295800</v>
+        <v>470288</v>
       </c>
       <c r="F55">
-        <v>9834382</v>
+        <v>4697702</v>
       </c>
       <c r="G55" t="str">
         <v>가짜지점</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-09-14 15:21:00</v>
+        <v>2026-09-11 15:21:00</v>
       </c>
       <c r="B56" t="str">
         <v>타행이체</v>
       </c>
       <c r="C56" t="str">
-        <v>BC카드매출</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D56" t="str">
         <v/>
       </c>
       <c r="E56">
-        <v>479180</v>
+        <v>39060</v>
       </c>
       <c r="F56">
-        <v>10313562</v>
+        <v>4736762</v>
       </c>
       <c r="G56" t="str">
         <v>가짜지점</v>
@@ -1645,22 +1645,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-09-14 16:32:00</v>
+        <v>2026-09-11 16:32:00</v>
       </c>
       <c r="B57" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C57" t="str">
-        <v>땡겨요정산</v>
-      </c>
-      <c r="D57" t="str">
-        <v/>
-      </c>
-      <c r="E57">
-        <v>159960</v>
+        <v>포장나라</v>
+      </c>
+      <c r="D57">
+        <v>340000</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
       </c>
       <c r="F57">
-        <v>10473522</v>
+        <v>4396762</v>
       </c>
       <c r="G57" t="str">
         <v>가짜지점</v>
@@ -1668,22 +1668,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-09-15 17:43:00</v>
+        <v>2026-09-12 17:43:00</v>
       </c>
       <c r="B58" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C58" t="str">
-        <v>요기요정산</v>
-      </c>
-      <c r="D58" t="str">
-        <v/>
-      </c>
-      <c r="E58">
-        <v>66220</v>
+        <v>새벽채소</v>
+      </c>
+      <c r="D58">
+        <v>270000</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
       </c>
       <c r="F58">
-        <v>10539742</v>
+        <v>4126762</v>
       </c>
       <c r="G58" t="str">
         <v>가짜지점</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-09-15 09:54:00</v>
+        <v>2026-09-12 09:54:00</v>
       </c>
       <c r="B59" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C59" t="str">
-        <v>쿠팡이츠정산</v>
-      </c>
-      <c r="D59" t="str">
-        <v/>
-      </c>
-      <c r="E59">
-        <v>157440</v>
+        <v>NH체크 (주)가짜유통</v>
+      </c>
+      <c r="D59">
+        <v>61800</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
       </c>
       <c r="F59">
-        <v>10697182</v>
+        <v>4064962</v>
       </c>
       <c r="G59" t="str">
         <v>가짜지점</v>
@@ -1714,22 +1714,22 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-09-15 10:05:00</v>
+        <v>2026-09-13 10:05:00</v>
       </c>
       <c r="B60" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C60" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D60" t="str">
-        <v/>
-      </c>
-      <c r="E60">
-        <v>301750</v>
+        <v>다라유통</v>
+      </c>
+      <c r="D60">
+        <v>760000</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
       </c>
       <c r="F60">
-        <v>10998932</v>
+        <v>3304962</v>
       </c>
       <c r="G60" t="str">
         <v>가짜지점</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-09-15 11:16:00</v>
+        <v>2026-09-13 11:16:00</v>
       </c>
       <c r="B61" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C61" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D61" t="str">
-        <v/>
-      </c>
-      <c r="E61">
-        <v>1957228</v>
+        <v>NH체크 가짜철물</v>
+      </c>
+      <c r="D61">
+        <v>15000</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
       </c>
       <c r="F61">
-        <v>12956160</v>
+        <v>3289962</v>
       </c>
       <c r="G61" t="str">
         <v>가짜지점</v>
@@ -1760,22 +1760,22 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-09-15 12:27:00</v>
+        <v>2026-09-14 12:27:00</v>
       </c>
       <c r="B62" t="str">
         <v>타행이체</v>
       </c>
       <c r="C62" t="str">
-        <v>땡겨요정산</v>
+        <v>요기요정산</v>
       </c>
       <c r="D62" t="str">
         <v/>
       </c>
       <c r="E62">
-        <v>32550</v>
+        <v>60200</v>
       </c>
       <c r="F62">
-        <v>12988710</v>
+        <v>3350162</v>
       </c>
       <c r="G62" t="str">
         <v>가짜지점</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-09-15 13:38:00</v>
+        <v>2026-09-14 13:38:00</v>
       </c>
       <c r="B63" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C63" t="str">
-        <v>생활비이체</v>
-      </c>
-      <c r="D63">
-        <v>2500000</v>
-      </c>
-      <c r="E63" t="str">
-        <v/>
+        <v>쿠팡이츠정산</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63">
+        <v>148420</v>
       </c>
       <c r="F63">
-        <v>10488710</v>
+        <v>3498582</v>
       </c>
       <c r="G63" t="str">
         <v>가짜지점</v>
@@ -1806,22 +1806,22 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-09-15 14:49:00</v>
+        <v>2026-09-14 14:49:00</v>
       </c>
       <c r="B64" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C64" t="str">
-        <v>NH체크 가짜마트</v>
-      </c>
-      <c r="D64">
-        <v>27900</v>
-      </c>
-      <c r="E64" t="str">
-        <v/>
+        <v>우아한형제들</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64">
+        <v>295800</v>
       </c>
       <c r="F64">
-        <v>10460810</v>
+        <v>3794382</v>
       </c>
       <c r="G64" t="str">
         <v>가짜지점</v>
@@ -1829,22 +1829,22 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-09-16 15:00:00</v>
+        <v>2026-09-14 15:00:00</v>
       </c>
       <c r="B65" t="str">
         <v>타행이체</v>
       </c>
       <c r="C65" t="str">
-        <v>요기요정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D65" t="str">
         <v/>
       </c>
       <c r="E65">
-        <v>70520</v>
+        <v>479180</v>
       </c>
       <c r="F65">
-        <v>10531330</v>
+        <v>4273562</v>
       </c>
       <c r="G65" t="str">
         <v>가짜지점</v>
@@ -1852,22 +1852,22 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-09-16 16:11:00</v>
+        <v>2026-09-14 16:11:00</v>
       </c>
       <c r="B66" t="str">
         <v>타행이체</v>
       </c>
       <c r="C66" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D66" t="str">
         <v/>
       </c>
       <c r="E66">
-        <v>160720</v>
+        <v>159960</v>
       </c>
       <c r="F66">
-        <v>10692050</v>
+        <v>4433522</v>
       </c>
       <c r="G66" t="str">
         <v>가짜지점</v>
@@ -1875,22 +1875,22 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-09-16 17:22:00</v>
+        <v>2026-09-15 17:22:00</v>
       </c>
       <c r="B67" t="str">
         <v>타행이체</v>
       </c>
       <c r="C67" t="str">
-        <v>우아한형제들</v>
+        <v>요기요정산</v>
       </c>
       <c r="D67" t="str">
         <v/>
       </c>
       <c r="E67">
-        <v>1230800</v>
+        <v>66220</v>
       </c>
       <c r="F67">
-        <v>11922850</v>
+        <v>4499742</v>
       </c>
       <c r="G67" t="str">
         <v>가짜지점</v>
@@ -1898,22 +1898,22 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-09-16 09:33:00</v>
+        <v>2026-09-15 09:33:00</v>
       </c>
       <c r="B68" t="str">
         <v>타행이체</v>
       </c>
       <c r="C68" t="str">
-        <v>BC카드매출</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D68" t="str">
         <v/>
       </c>
       <c r="E68">
-        <v>400140</v>
+        <v>157440</v>
       </c>
       <c r="F68">
-        <v>12322990</v>
+        <v>4657182</v>
       </c>
       <c r="G68" t="str">
         <v>가짜지점</v>
@@ -1921,22 +1921,22 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-09-16 10:44:00</v>
+        <v>2026-09-15 10:44:00</v>
       </c>
       <c r="B69" t="str">
         <v>타행이체</v>
       </c>
       <c r="C69" t="str">
-        <v>땡겨요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D69" t="str">
         <v/>
       </c>
       <c r="E69">
-        <v>33480</v>
+        <v>301750</v>
       </c>
       <c r="F69">
-        <v>12356470</v>
+        <v>4958932</v>
       </c>
       <c r="G69" t="str">
         <v>가짜지점</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-09-16 11:55:00</v>
+        <v>2026-09-15 11:55:00</v>
       </c>
       <c r="B70" t="str">
-        <v>인터넷</v>
+        <v>타행이체</v>
       </c>
       <c r="C70" t="str">
-        <v>NH체크 가짜주차</v>
-      </c>
-      <c r="D70">
-        <v>7000</v>
-      </c>
-      <c r="E70" t="str">
-        <v/>
+        <v>BC카드매출</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70">
+        <v>1957228</v>
       </c>
       <c r="F70">
-        <v>12349470</v>
+        <v>6916160</v>
       </c>
       <c r="G70" t="str">
         <v>가짜지점</v>
@@ -1967,22 +1967,22 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-09-17 12:06:00</v>
+        <v>2026-09-15 12:06:00</v>
       </c>
       <c r="B71" t="str">
         <v>타행이체</v>
       </c>
       <c r="C71" t="str">
-        <v>요기요정산</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D71" t="str">
         <v/>
       </c>
       <c r="E71">
-        <v>72240</v>
+        <v>32550</v>
       </c>
       <c r="F71">
-        <v>12421710</v>
+        <v>6948710</v>
       </c>
       <c r="G71" t="str">
         <v>가짜지점</v>
@@ -1990,22 +1990,22 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-09-17 13:17:00</v>
+        <v>2026-09-15 13:17:00</v>
       </c>
       <c r="B72" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C72" t="str">
-        <v>쿠팡이츠정산</v>
-      </c>
-      <c r="D72" t="str">
-        <v/>
-      </c>
-      <c r="E72">
-        <v>656000</v>
+        <v>생활비이체</v>
+      </c>
+      <c r="D72">
+        <v>2500000</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
       </c>
       <c r="F72">
-        <v>13077710</v>
+        <v>4448710</v>
       </c>
       <c r="G72" t="str">
         <v>가짜지점</v>
@@ -2013,22 +2013,22 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-09-17 14:28:00</v>
+        <v>2026-09-15 14:28:00</v>
       </c>
       <c r="B73" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C73" t="str">
-        <v>우아한형제들</v>
-      </c>
-      <c r="D73" t="str">
-        <v/>
-      </c>
-      <c r="E73">
-        <v>251600</v>
+        <v>NH체크 가짜마트</v>
+      </c>
+      <c r="D73">
+        <v>27900</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
       </c>
       <c r="F73">
-        <v>13329310</v>
+        <v>4420810</v>
       </c>
       <c r="G73" t="str">
         <v>가짜지점</v>
@@ -2036,22 +2036,22 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026-09-17 15:39:00</v>
+        <v>2026-09-16 15:39:00</v>
       </c>
       <c r="B74" t="str">
         <v>타행이체</v>
       </c>
       <c r="C74" t="str">
-        <v>BC카드매출</v>
+        <v>요기요정산</v>
       </c>
       <c r="D74" t="str">
         <v/>
       </c>
       <c r="E74">
-        <v>411008</v>
+        <v>70520</v>
       </c>
       <c r="F74">
-        <v>13740318</v>
+        <v>4491330</v>
       </c>
       <c r="G74" t="str">
         <v>가짜지점</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026-09-17 16:50:00</v>
+        <v>2026-09-16 16:50:00</v>
       </c>
       <c r="B75" t="str">
         <v>타행이체</v>
       </c>
       <c r="C75" t="str">
-        <v>땡겨요정산</v>
+        <v>쿠팡이츠정산</v>
       </c>
       <c r="D75" t="str">
         <v/>
       </c>
       <c r="E75">
-        <v>35340</v>
+        <v>160720</v>
       </c>
       <c r="F75">
-        <v>13775658</v>
+        <v>4652050</v>
       </c>
       <c r="G75" t="str">
         <v>가짜지점</v>
@@ -2082,22 +2082,22 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026-09-18 17:01:00</v>
+        <v>2026-09-16 17:01:00</v>
       </c>
       <c r="B76" t="str">
         <v>타행이체</v>
       </c>
       <c r="C76" t="str">
-        <v>요기요정산</v>
+        <v>우아한형제들</v>
       </c>
       <c r="D76" t="str">
         <v/>
       </c>
       <c r="E76">
-        <v>294980</v>
+        <v>1230800</v>
       </c>
       <c r="F76">
-        <v>14070638</v>
+        <v>5882850</v>
       </c>
       <c r="G76" t="str">
         <v>가짜지점</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026-09-18 09:12:00</v>
+        <v>2026-09-16 09:12:00</v>
       </c>
       <c r="B77" t="str">
         <v>타행이체</v>
       </c>
       <c r="C77" t="str">
-        <v>쿠팡이츠정산</v>
+        <v>BC카드매출</v>
       </c>
       <c r="D77" t="str">
         <v/>
       </c>
       <c r="E77">
-        <v>133660</v>
+        <v>400140</v>
       </c>
       <c r="F77">
-        <v>14204298</v>
+        <v>6282990</v>
       </c>
       <c r="G77" t="str">
         <v>가짜지점</v>
@@ -2128,22 +2128,22 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026-09-18 10:23:00</v>
+        <v>2026-09-16 10:23:00</v>
       </c>
       <c r="B78" t="str">
         <v>타행이체</v>
       </c>
       <c r="C78" t="str">
-        <v>우아한형제들</v>
+        <v>땡겨요정산</v>
       </c>
       <c r="D78" t="str">
         <v/>
       </c>
       <c r="E78">
-        <v>258400</v>
+        <v>33480</v>
       </c>
       <c r="F78">
-        <v>14462698</v>
+        <v>6316470</v>
       </c>
       <c r="G78" t="str">
         <v>가짜지점</v>
@@ -2151,22 +2151,22 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026-09-18 11:34:00</v>
+        <v>2026-09-16 11:34:00</v>
       </c>
       <c r="B79" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C79" t="str">
-        <v>BC카드매출</v>
-      </c>
-      <c r="D79" t="str">
-        <v/>
-      </c>
-      <c r="E79">
-        <v>437684</v>
+        <v>바로고 배달대행</v>
+      </c>
+      <c r="D79">
+        <v>800000</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
       </c>
       <c r="F79">
-        <v>14900382</v>
+        <v>5516470</v>
       </c>
       <c r="G79" t="str">
         <v>가짜지점</v>
@@ -2174,30 +2174,329 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026-09-18 12:45:00</v>
+        <v>2026-09-16 12:45:00</v>
       </c>
       <c r="B80" t="str">
-        <v>타행이체</v>
+        <v>인터넷</v>
       </c>
       <c r="C80" t="str">
+        <v>NH체크 가짜주차</v>
+      </c>
+      <c r="D80">
+        <v>7000</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80">
+        <v>5509470</v>
+      </c>
+      <c r="G80" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2026-09-17 13:56:00</v>
+      </c>
+      <c r="B81" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C81" t="str">
+        <v>요기요정산</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81">
+        <v>72240</v>
+      </c>
+      <c r="F81">
+        <v>5581710</v>
+      </c>
+      <c r="G81" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2026-09-17 14:07:00</v>
+      </c>
+      <c r="B82" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C82" t="str">
+        <v>쿠팡이츠정산</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82">
+        <v>656000</v>
+      </c>
+      <c r="F82">
+        <v>6237710</v>
+      </c>
+      <c r="G82" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2026-09-17 15:18:00</v>
+      </c>
+      <c r="B83" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C83" t="str">
+        <v>우아한형제들</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83">
+        <v>251600</v>
+      </c>
+      <c r="F83">
+        <v>6489310</v>
+      </c>
+      <c r="G83" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2026-09-17 16:29:00</v>
+      </c>
+      <c r="B84" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C84" t="str">
+        <v>BC카드매출</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84">
+        <v>411008</v>
+      </c>
+      <c r="F84">
+        <v>6900318</v>
+      </c>
+      <c r="G84" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2026-09-17 17:40:00</v>
+      </c>
+      <c r="B85" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C85" t="str">
         <v>땡겨요정산</v>
       </c>
-      <c r="D80" t="str">
-        <v/>
-      </c>
-      <c r="E80">
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85">
+        <v>35340</v>
+      </c>
+      <c r="F85">
+        <v>6935658</v>
+      </c>
+      <c r="G85" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2026-09-17 09:51:00</v>
+      </c>
+      <c r="B86" t="str">
+        <v>인터넷</v>
+      </c>
+      <c r="C86" t="str">
+        <v>가나식품</v>
+      </c>
+      <c r="D86">
+        <v>1480000</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86">
+        <v>5455658</v>
+      </c>
+      <c r="G86" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2026-09-18 10:02:00</v>
+      </c>
+      <c r="B87" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C87" t="str">
+        <v>요기요정산</v>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87">
+        <v>294980</v>
+      </c>
+      <c r="F87">
+        <v>5750638</v>
+      </c>
+      <c r="G87" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2026-09-18 11:13:00</v>
+      </c>
+      <c r="B88" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C88" t="str">
+        <v>쿠팡이츠정산</v>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88">
+        <v>133660</v>
+      </c>
+      <c r="F88">
+        <v>5884298</v>
+      </c>
+      <c r="G88" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2026-09-18 12:24:00</v>
+      </c>
+      <c r="B89" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C89" t="str">
+        <v>우아한형제들</v>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89">
+        <v>258400</v>
+      </c>
+      <c r="F89">
+        <v>6142698</v>
+      </c>
+      <c r="G89" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2026-09-18 13:35:00</v>
+      </c>
+      <c r="B90" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C90" t="str">
+        <v>BC카드매출</v>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90">
+        <v>437684</v>
+      </c>
+      <c r="F90">
+        <v>6580382</v>
+      </c>
+      <c r="G90" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>2026-09-18 14:46:00</v>
+      </c>
+      <c r="B91" t="str">
+        <v>타행이체</v>
+      </c>
+      <c r="C91" t="str">
+        <v>땡겨요정산</v>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91">
         <v>40920</v>
       </c>
-      <c r="F80">
-        <v>14941302</v>
-      </c>
-      <c r="G80" t="str">
+      <c r="F91">
+        <v>6621302</v>
+      </c>
+      <c r="G91" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2026-09-18 15:57:00</v>
+      </c>
+      <c r="B92" t="str">
+        <v>인터넷</v>
+      </c>
+      <c r="C92" t="str">
+        <v>한국전력</v>
+      </c>
+      <c r="D92">
+        <v>260000</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92">
+        <v>6361302</v>
+      </c>
+      <c r="G92" t="str">
+        <v>가짜지점</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>2026-09-18 16:08:00</v>
+      </c>
+      <c r="B93" t="str">
+        <v>인터넷</v>
+      </c>
+      <c r="C93" t="str">
+        <v>도시가스</v>
+      </c>
+      <c r="D93">
+        <v>120000</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93">
+        <v>6241302</v>
+      </c>
+      <c r="G93" t="str">
         <v>가짜지점</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G80"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G93"/>
   </ignoredErrors>
 </worksheet>
 </file>